--- a/research/traditional_assets/database/data/uganda/uganda_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/uganda/uganda_telecom_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1151013756164026</v>
+        <v>0.1147875714895534</v>
       </c>
       <c r="C2">
-        <v>2055.721643505271</v>
+        <v>2041.556182360019</v>
       </c>
       <c r="D2">
-        <v>2005.321643505272</v>
+        <v>2011.246182360019</v>
       </c>
       <c r="E2">
-        <v>-346.6</v>
+        <v>-326.51</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>20.09</v>
       </c>
       <c r="G2">
         <v>50.4</v>
@@ -1439,28 +1439,28 @@
         <v>329.65</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.010527</v>
       </c>
       <c r="N2">
-        <v>329.65</v>
+        <v>328.639473</v>
       </c>
       <c r="O2">
-        <v>98.895</v>
+        <v>98.59184189999998</v>
       </c>
       <c r="P2">
-        <v>230.755</v>
+        <v>230.0476311</v>
       </c>
       <c r="Q2">
-        <v>362.855</v>
+        <v>362.1476311</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1151013756164026</v>
+        <v>0.1155913853429832</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5365156846091585</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>326.2159249579674</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1147875714895534</v>
+        <v>0.1144737673627042</v>
       </c>
       <c r="C3">
-        <v>2041.556182360019</v>
+        <v>2027.42583195946</v>
       </c>
       <c r="D3">
-        <v>2011.246182360019</v>
+        <v>2017.20583195946</v>
       </c>
       <c r="E3">
-        <v>-326.51</v>
+        <v>-306.42</v>
       </c>
       <c r="F3">
-        <v>20.09</v>
+        <v>40.18</v>
       </c>
       <c r="G3">
         <v>50.4</v>
@@ -1521,28 +1521,28 @@
         <v>329.65</v>
       </c>
       <c r="M3">
-        <v>1.010527</v>
+        <v>2.021054</v>
       </c>
       <c r="N3">
-        <v>328.639473</v>
+        <v>327.628946</v>
       </c>
       <c r="O3">
-        <v>98.59184189999998</v>
+        <v>98.28868379999999</v>
       </c>
       <c r="P3">
-        <v>230.0476311</v>
+        <v>229.3402622</v>
       </c>
       <c r="Q3">
-        <v>362.1476311</v>
+        <v>361.4402622</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1155913853429832</v>
+        <v>0.1160913952680655</v>
       </c>
       <c r="T3">
-        <v>0.5365156846091585</v>
+        <v>0.5403594708579704</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>326.2159249579674</v>
+        <v>163.1079624789838</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1144737673627042</v>
+        <v>0.114159963235855</v>
       </c>
       <c r="C4">
-        <v>2027.42583195946</v>
+        <v>2013.330905347739</v>
       </c>
       <c r="D4">
-        <v>2017.20583195946</v>
+        <v>2023.200905347739</v>
       </c>
       <c r="E4">
-        <v>-306.42</v>
+        <v>-286.33</v>
       </c>
       <c r="F4">
-        <v>40.18</v>
+        <v>60.27</v>
       </c>
       <c r="G4">
         <v>50.4</v>
@@ -1603,28 +1603,28 @@
         <v>329.65</v>
       </c>
       <c r="M4">
-        <v>2.021054</v>
+        <v>3.031581</v>
       </c>
       <c r="N4">
-        <v>327.628946</v>
+        <v>326.618419</v>
       </c>
       <c r="O4">
-        <v>98.28868379999999</v>
+        <v>97.98552569999998</v>
       </c>
       <c r="P4">
-        <v>229.3402622</v>
+        <v>228.6328933</v>
       </c>
       <c r="Q4">
-        <v>361.4402622</v>
+        <v>360.7328933</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1160913952680655</v>
+        <v>0.1166017146761391</v>
       </c>
       <c r="T4">
-        <v>0.5403594708579704</v>
+        <v>0.5442825104315</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>163.1079624789838</v>
+        <v>108.7386416526558</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.114159963235855</v>
+        <v>0.1138461591090058</v>
       </c>
       <c r="C5">
-        <v>2013.330905347739</v>
+        <v>1999.271719301523</v>
       </c>
       <c r="D5">
-        <v>2023.200905347739</v>
+        <v>2029.231719301523</v>
       </c>
       <c r="E5">
-        <v>-286.33</v>
+        <v>-266.24</v>
       </c>
       <c r="F5">
-        <v>60.27</v>
+        <v>80.36</v>
       </c>
       <c r="G5">
         <v>50.4</v>
@@ -1685,28 +1685,28 @@
         <v>329.65</v>
       </c>
       <c r="M5">
-        <v>3.031581</v>
+        <v>4.042108</v>
       </c>
       <c r="N5">
-        <v>326.618419</v>
+        <v>325.607892</v>
       </c>
       <c r="O5">
-        <v>97.98552569999998</v>
+        <v>97.68236759999999</v>
       </c>
       <c r="P5">
-        <v>228.6328933</v>
+        <v>227.9255244</v>
       </c>
       <c r="Q5">
-        <v>360.7328933</v>
+        <v>360.0255244</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1166017146761391</v>
+        <v>0.1171226657385477</v>
       </c>
       <c r="T5">
-        <v>0.5442825104315</v>
+        <v>0.5482872799961448</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>108.7386416526558</v>
+        <v>81.55398123949188</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1138461591090058</v>
+        <v>0.1135323549821565</v>
       </c>
       <c r="C6">
-        <v>1999.271719301523</v>
+        <v>1985.2485943858</v>
       </c>
       <c r="D6">
-        <v>2029.231719301523</v>
+        <v>2035.2985943858</v>
       </c>
       <c r="E6">
-        <v>-266.24</v>
+        <v>-246.15</v>
       </c>
       <c r="F6">
-        <v>80.36</v>
+        <v>100.45</v>
       </c>
       <c r="G6">
         <v>50.4</v>
@@ -1767,28 +1767,28 @@
         <v>329.65</v>
       </c>
       <c r="M6">
-        <v>4.042108</v>
+        <v>5.052635</v>
       </c>
       <c r="N6">
-        <v>325.607892</v>
+        <v>324.597365</v>
       </c>
       <c r="O6">
-        <v>97.68236759999999</v>
+        <v>97.37920949999999</v>
       </c>
       <c r="P6">
-        <v>227.9255244</v>
+        <v>227.2181555</v>
       </c>
       <c r="Q6">
-        <v>360.0255244</v>
+        <v>359.3181555</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1171226657385477</v>
+        <v>0.1176545841917437</v>
       </c>
       <c r="T6">
-        <v>0.5482872799961448</v>
+        <v>0.5523763604989926</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>81.55398123949188</v>
+        <v>65.24318499159349</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1135323549821565</v>
+        <v>0.1132185508553073</v>
       </c>
       <c r="C7">
-        <v>1985.2485943858</v>
+        <v>1971.261855010674</v>
       </c>
       <c r="D7">
-        <v>2035.2985943858</v>
+        <v>2041.401855010674</v>
       </c>
       <c r="E7">
-        <v>-246.15</v>
+        <v>-226.06</v>
       </c>
       <c r="F7">
-        <v>100.45</v>
+        <v>120.54</v>
       </c>
       <c r="G7">
         <v>50.4</v>
@@ -1849,28 +1849,28 @@
         <v>329.65</v>
       </c>
       <c r="M7">
-        <v>5.052635</v>
+        <v>6.063162</v>
       </c>
       <c r="N7">
-        <v>324.597365</v>
+        <v>323.586838</v>
       </c>
       <c r="O7">
-        <v>97.37920949999999</v>
+        <v>97.0760514</v>
       </c>
       <c r="P7">
-        <v>227.2181555</v>
+        <v>226.5107866</v>
       </c>
       <c r="Q7">
-        <v>359.3181555</v>
+        <v>358.6107866</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1176545841917437</v>
+        <v>0.1181978200588376</v>
       </c>
       <c r="T7">
-        <v>0.5523763604989926</v>
+        <v>0.5565524427146671</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>65.24318499159349</v>
+        <v>54.36932082632791</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1132185508553073</v>
+        <v>0.1129047467284581</v>
       </c>
       <c r="C8">
-        <v>1971.261855010674</v>
+        <v>1957.311829489198</v>
       </c>
       <c r="D8">
-        <v>2041.401855010674</v>
+        <v>2047.541829489199</v>
       </c>
       <c r="E8">
-        <v>-226.06</v>
+        <v>-205.97</v>
       </c>
       <c r="F8">
-        <v>120.54</v>
+        <v>140.63</v>
       </c>
       <c r="G8">
         <v>50.4</v>
@@ -1931,28 +1931,28 @@
         <v>329.65</v>
       </c>
       <c r="M8">
-        <v>6.063161999999999</v>
+        <v>7.073688999999999</v>
       </c>
       <c r="N8">
-        <v>323.586838</v>
+        <v>322.576311</v>
       </c>
       <c r="O8">
-        <v>97.0760514</v>
+        <v>96.77289329999999</v>
       </c>
       <c r="P8">
-        <v>226.5107866</v>
+        <v>225.8034177</v>
       </c>
       <c r="Q8">
-        <v>358.6107866</v>
+        <v>357.9034177</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1181978200588376</v>
+        <v>0.1187527384176969</v>
       </c>
       <c r="T8">
-        <v>0.5565524427146671</v>
+        <v>0.5608183331500335</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>54.36932082632792</v>
+        <v>46.60227499399536</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1129047467284581</v>
+        <v>0.1125909426016089</v>
       </c>
       <c r="C9">
-        <v>1957.311829489198</v>
+        <v>1943.398850096241</v>
       </c>
       <c r="D9">
-        <v>2047.541829489199</v>
+        <v>2053.718850096241</v>
       </c>
       <c r="E9">
-        <v>-205.97</v>
+        <v>-185.88</v>
       </c>
       <c r="F9">
-        <v>140.63</v>
+        <v>160.72</v>
       </c>
       <c r="G9">
         <v>50.4</v>
@@ -2013,28 +2013,28 @@
         <v>329.65</v>
       </c>
       <c r="M9">
-        <v>7.073689000000001</v>
+        <v>8.084216</v>
       </c>
       <c r="N9">
-        <v>322.576311</v>
+        <v>321.565784</v>
       </c>
       <c r="O9">
-        <v>96.77289329999999</v>
+        <v>96.46973519999999</v>
       </c>
       <c r="P9">
-        <v>225.8034177</v>
+        <v>225.0960487999999</v>
       </c>
       <c r="Q9">
-        <v>357.9034177</v>
+        <v>357.1960488</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1187527384176969</v>
+        <v>0.1193197202191401</v>
       </c>
       <c r="T9">
-        <v>0.5608183331500335</v>
+        <v>0.5651769603339948</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>46.60227499399534</v>
+        <v>40.77699061974593</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1125909426016089</v>
+        <v>0.1122771384747597</v>
       </c>
       <c r="C10">
-        <v>1943.398850096241</v>
+        <v>1929.523253128427</v>
       </c>
       <c r="D10">
-        <v>2053.718850096241</v>
+        <v>2059.933253128427</v>
       </c>
       <c r="E10">
-        <v>-185.88</v>
+        <v>-165.79</v>
       </c>
       <c r="F10">
-        <v>160.72</v>
+        <v>180.81</v>
       </c>
       <c r="G10">
         <v>50.4</v>
@@ -2095,28 +2095,28 @@
         <v>329.65</v>
       </c>
       <c r="M10">
-        <v>8.084216</v>
+        <v>9.094742999999999</v>
       </c>
       <c r="N10">
-        <v>321.565784</v>
+        <v>320.555257</v>
       </c>
       <c r="O10">
-        <v>96.46973519999999</v>
+        <v>96.1665771</v>
       </c>
       <c r="P10">
-        <v>225.0960487999999</v>
+        <v>224.3886799</v>
       </c>
       <c r="Q10">
-        <v>357.1960488</v>
+        <v>356.4886799</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1193197202191401</v>
+        <v>0.1198991631590766</v>
       </c>
       <c r="T10">
-        <v>0.5651769603339948</v>
+        <v>0.5696313815219991</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>40.77699061974593</v>
+        <v>36.24621388421861</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1122771384747597</v>
+        <v>0.1119633343479105</v>
       </c>
       <c r="C11">
-        <v>1929.523253128427</v>
+        <v>1915.685378965174</v>
       </c>
       <c r="D11">
-        <v>2059.933253128427</v>
+        <v>2066.185378965174</v>
       </c>
       <c r="E11">
-        <v>-165.79</v>
+        <v>-145.7</v>
       </c>
       <c r="F11">
-        <v>180.81</v>
+        <v>200.9</v>
       </c>
       <c r="G11">
         <v>50.4</v>
@@ -2177,28 +2177,28 @@
         <v>329.65</v>
       </c>
       <c r="M11">
-        <v>9.094742999999999</v>
+        <v>10.10527</v>
       </c>
       <c r="N11">
-        <v>320.555257</v>
+        <v>319.54473</v>
       </c>
       <c r="O11">
-        <v>96.1665771</v>
+        <v>95.86341899999998</v>
       </c>
       <c r="P11">
-        <v>224.3886799</v>
+        <v>223.681311</v>
       </c>
       <c r="Q11">
-        <v>356.4886799</v>
+        <v>355.781311</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1198991631590766</v>
+        <v>0.1204914826087894</v>
       </c>
       <c r="T11">
-        <v>0.5696313815219991</v>
+        <v>0.5741847898475148</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>36.24621388421861</v>
+        <v>32.62159249579675</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1119633343479105</v>
+        <v>0.1116495302210613</v>
       </c>
       <c r="C12">
-        <v>1915.685378965174</v>
+        <v>1901.885572130834</v>
       </c>
       <c r="D12">
-        <v>2066.185378965174</v>
+        <v>2072.475572130834</v>
       </c>
       <c r="E12">
-        <v>-145.7</v>
+        <v>-125.61</v>
       </c>
       <c r="F12">
-        <v>200.9</v>
+        <v>220.99</v>
       </c>
       <c r="G12">
         <v>50.4</v>
@@ -2259,28 +2259,28 @@
         <v>329.65</v>
       </c>
       <c r="M12">
-        <v>10.10527</v>
+        <v>11.115797</v>
       </c>
       <c r="N12">
-        <v>319.54473</v>
+        <v>318.534203</v>
       </c>
       <c r="O12">
-        <v>95.86341899999998</v>
+        <v>95.56026089999999</v>
       </c>
       <c r="P12">
-        <v>223.681311</v>
+        <v>222.9739421</v>
       </c>
       <c r="Q12">
-        <v>355.781311</v>
+        <v>355.0739421</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1204914826087894</v>
+        <v>0.121097112607934</v>
       </c>
       <c r="T12">
-        <v>0.5741847898475148</v>
+        <v>0.5788405219556262</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.62159249579675</v>
+        <v>29.65599317799704</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1116495302210613</v>
+        <v>0.1113357260942121</v>
       </c>
       <c r="C13">
-        <v>1901.885572130834</v>
+        <v>1888.124181357986</v>
       </c>
       <c r="D13">
-        <v>2072.475572130834</v>
+        <v>2078.804181357986</v>
       </c>
       <c r="E13">
-        <v>-125.61</v>
+        <v>-105.52</v>
       </c>
       <c r="F13">
-        <v>220.99</v>
+        <v>241.08</v>
       </c>
       <c r="G13">
         <v>50.4</v>
@@ -2341,28 +2341,28 @@
         <v>329.65</v>
       </c>
       <c r="M13">
-        <v>11.115797</v>
+        <v>12.126324</v>
       </c>
       <c r="N13">
-        <v>318.534203</v>
+        <v>317.523676</v>
       </c>
       <c r="O13">
-        <v>95.56026089999999</v>
+        <v>95.25710279999998</v>
       </c>
       <c r="P13">
-        <v>222.9739421</v>
+        <v>222.2665732</v>
       </c>
       <c r="Q13">
-        <v>355.0739421</v>
+        <v>354.3665731999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.121097112607934</v>
+        <v>0.121716506925241</v>
       </c>
       <c r="T13">
-        <v>0.5788405219556262</v>
+        <v>0.5836020661571037</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.65599317799704</v>
+        <v>27.18466041316396</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1113357260942121</v>
+        <v>0.1110219219673629</v>
       </c>
       <c r="C14">
-        <v>1888.124181357986</v>
+        <v>1874.401559651878</v>
       </c>
       <c r="D14">
-        <v>2078.804181357986</v>
+        <v>2085.171559651877</v>
       </c>
       <c r="E14">
-        <v>-105.52</v>
+        <v>-85.43000000000001</v>
       </c>
       <c r="F14">
-        <v>241.08</v>
+        <v>261.17</v>
       </c>
       <c r="G14">
         <v>50.4</v>
@@ -2423,28 +2423,28 @@
         <v>329.65</v>
       </c>
       <c r="M14">
-        <v>12.126324</v>
+        <v>13.136851</v>
       </c>
       <c r="N14">
-        <v>317.523676</v>
+        <v>316.513149</v>
       </c>
       <c r="O14">
-        <v>95.25710279999998</v>
+        <v>94.95394469999999</v>
       </c>
       <c r="P14">
-        <v>222.2665732</v>
+        <v>221.5592043</v>
       </c>
       <c r="Q14">
-        <v>354.3665731999999</v>
+        <v>353.6592043</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.121716506925241</v>
+        <v>0.1223501401923711</v>
       </c>
       <c r="T14">
-        <v>0.5836020661571037</v>
+        <v>0.5884730711448222</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.18466041316396</v>
+        <v>25.09353268907442</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1110219219673629</v>
+        <v>0.1107081178405137</v>
       </c>
       <c r="C15">
-        <v>1874.401559651878</v>
+        <v>1860.718064356069</v>
       </c>
       <c r="D15">
-        <v>2085.171559651877</v>
+        <v>2091.578064356069</v>
       </c>
       <c r="E15">
-        <v>-85.43000000000001</v>
+        <v>-65.33999999999997</v>
       </c>
       <c r="F15">
-        <v>261.17</v>
+        <v>281.26</v>
       </c>
       <c r="G15">
         <v>50.4</v>
@@ -2505,28 +2505,28 @@
         <v>329.65</v>
       </c>
       <c r="M15">
-        <v>13.136851</v>
+        <v>14.147378</v>
       </c>
       <c r="N15">
-        <v>316.513149</v>
+        <v>315.502622</v>
       </c>
       <c r="O15">
-        <v>94.95394469999999</v>
+        <v>94.65078659999999</v>
       </c>
       <c r="P15">
-        <v>221.5592043</v>
+        <v>220.8518354</v>
       </c>
       <c r="Q15">
-        <v>353.6592043</v>
+        <v>352.9518353999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1223501401923711</v>
+        <v>0.1229985091168763</v>
       </c>
       <c r="T15">
-        <v>0.5884730711448222</v>
+        <v>0.5934573553183016</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.09353268907442</v>
+        <v>23.30113749699767</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1107081178405137</v>
+        <v>0.1103943137136645</v>
       </c>
       <c r="C16">
-        <v>1860.718064356069</v>
+        <v>1847.074057219277</v>
       </c>
       <c r="D16">
-        <v>2091.578064356069</v>
+        <v>2098.024057219277</v>
       </c>
       <c r="E16">
-        <v>-65.33999999999997</v>
+        <v>-45.25</v>
       </c>
       <c r="F16">
-        <v>281.26</v>
+        <v>301.35</v>
       </c>
       <c r="G16">
         <v>50.4</v>
@@ -2587,28 +2587,28 @@
         <v>329.65</v>
       </c>
       <c r="M16">
-        <v>14.147378</v>
+        <v>15.157905</v>
       </c>
       <c r="N16">
-        <v>315.502622</v>
+        <v>314.4920949999999</v>
       </c>
       <c r="O16">
-        <v>94.65078659999999</v>
+        <v>94.34762849999998</v>
       </c>
       <c r="P16">
-        <v>220.8518354</v>
+        <v>220.1444665</v>
       </c>
       <c r="Q16">
-        <v>352.9518353999999</v>
+        <v>352.2444664999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1229985091168763</v>
+        <v>0.1236621337807817</v>
       </c>
       <c r="T16">
-        <v>0.5934573553183016</v>
+        <v>0.5985589167664511</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.30113749699767</v>
+        <v>21.74772833053116</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1103943137136645</v>
+        <v>0.1100805095868153</v>
       </c>
       <c r="C17">
-        <v>1847.074057219277</v>
+        <v>1833.469904463471</v>
       </c>
       <c r="D17">
-        <v>2098.024057219277</v>
+        <v>2104.509904463471</v>
       </c>
       <c r="E17">
-        <v>-45.25000000000006</v>
+        <v>-25.16000000000003</v>
       </c>
       <c r="F17">
-        <v>301.35</v>
+        <v>321.44</v>
       </c>
       <c r="G17">
         <v>50.4</v>
@@ -2669,28 +2669,28 @@
         <v>329.65</v>
       </c>
       <c r="M17">
-        <v>15.157905</v>
+        <v>16.168432</v>
       </c>
       <c r="N17">
-        <v>314.492095</v>
+        <v>313.481568</v>
       </c>
       <c r="O17">
-        <v>94.3476285</v>
+        <v>94.04447039999999</v>
       </c>
       <c r="P17">
-        <v>220.1444665</v>
+        <v>219.4370976</v>
       </c>
       <c r="Q17">
-        <v>352.2444665</v>
+        <v>351.5370976</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1236621337807817</v>
+        <v>0.1243415590319229</v>
       </c>
       <c r="T17">
-        <v>0.5985589167664511</v>
+        <v>0.603781943963366</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.74772833053117</v>
+        <v>20.38849530987297</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1100805095868153</v>
+        <v>0.109766705459966</v>
       </c>
       <c r="C18">
-        <v>1833.469904463471</v>
+        <v>1819.905976853231</v>
       </c>
       <c r="D18">
-        <v>2104.509904463471</v>
+        <v>2111.035976853231</v>
       </c>
       <c r="E18">
-        <v>-25.16000000000003</v>
+        <v>-5.069999999999993</v>
       </c>
       <c r="F18">
-        <v>321.44</v>
+        <v>341.53</v>
       </c>
       <c r="G18">
         <v>50.4</v>
@@ -2751,28 +2751,28 @@
         <v>329.65</v>
       </c>
       <c r="M18">
-        <v>16.168432</v>
+        <v>17.178959</v>
       </c>
       <c r="N18">
-        <v>313.481568</v>
+        <v>312.471041</v>
       </c>
       <c r="O18">
-        <v>94.04447039999999</v>
+        <v>93.74131229999999</v>
       </c>
       <c r="P18">
-        <v>219.4370976</v>
+        <v>218.7297287</v>
       </c>
       <c r="Q18">
-        <v>351.5370976</v>
+        <v>350.8297286999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1243415590319229</v>
+        <v>0.1250373559758627</v>
       </c>
       <c r="T18">
-        <v>0.603781943963366</v>
+        <v>0.609130827237315</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.38849530987297</v>
+        <v>19.18917205635103</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.109766705459966</v>
+        <v>0.1094529013331168</v>
       </c>
       <c r="C19">
-        <v>1819.905976853231</v>
+        <v>1806.382649766393</v>
       </c>
       <c r="D19">
-        <v>2111.035976853231</v>
+        <v>2117.602649766393</v>
       </c>
       <c r="E19">
-        <v>-5.069999999999993</v>
+        <v>15.02000000000004</v>
       </c>
       <c r="F19">
-        <v>341.53</v>
+        <v>361.6200000000001</v>
       </c>
       <c r="G19">
         <v>50.4</v>
@@ -2833,28 +2833,28 @@
         <v>329.65</v>
       </c>
       <c r="M19">
-        <v>17.178959</v>
+        <v>18.189486</v>
       </c>
       <c r="N19">
-        <v>312.471041</v>
+        <v>311.460514</v>
       </c>
       <c r="O19">
-        <v>93.74131229999999</v>
+        <v>93.4381542</v>
       </c>
       <c r="P19">
-        <v>218.7297287</v>
+        <v>218.0223598</v>
       </c>
       <c r="Q19">
-        <v>350.8297286999999</v>
+        <v>350.1223598</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1250373559758627</v>
+        <v>0.1257501235769718</v>
       </c>
       <c r="T19">
-        <v>0.609130827237315</v>
+        <v>0.6146101710789214</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.18917205635103</v>
+        <v>18.1231069421093</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1094529013331169</v>
+        <v>0.1091390972062676</v>
       </c>
       <c r="C20">
-        <v>1806.382649766393</v>
+        <v>1792.900303266031</v>
       </c>
       <c r="D20">
-        <v>2117.602649766392</v>
+        <v>2124.210303266031</v>
       </c>
       <c r="E20">
-        <v>15.01999999999998</v>
+        <v>35.10999999999996</v>
       </c>
       <c r="F20">
-        <v>361.62</v>
+        <v>381.71</v>
       </c>
       <c r="G20">
         <v>50.4</v>
@@ -2915,28 +2915,28 @@
         <v>329.65</v>
       </c>
       <c r="M20">
-        <v>18.189486</v>
+        <v>19.200013</v>
       </c>
       <c r="N20">
-        <v>311.460514</v>
+        <v>310.449987</v>
       </c>
       <c r="O20">
-        <v>93.4381542</v>
+        <v>93.13499609999998</v>
       </c>
       <c r="P20">
-        <v>218.0223598</v>
+        <v>217.3149909</v>
       </c>
       <c r="Q20">
-        <v>350.1223598</v>
+        <v>349.4149909</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1257501235769718</v>
+        <v>0.1264804903781082</v>
       </c>
       <c r="T20">
-        <v>0.6146101710789214</v>
+        <v>0.6202248073610611</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.12310694210931</v>
+        <v>17.16925920831408</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1091390972062676</v>
+        <v>0.1088252930794184</v>
       </c>
       <c r="C21">
-        <v>1792.900303266031</v>
+        <v>1779.459322173782</v>
       </c>
       <c r="D21">
-        <v>2124.210303266031</v>
+        <v>2130.859322173781</v>
       </c>
       <c r="E21">
-        <v>35.10999999999996</v>
+        <v>55.19999999999999</v>
       </c>
       <c r="F21">
-        <v>381.71</v>
+        <v>401.8</v>
       </c>
       <c r="G21">
         <v>50.4</v>
@@ -2997,28 +2997,28 @@
         <v>329.65</v>
       </c>
       <c r="M21">
-        <v>19.200013</v>
+        <v>20.21054</v>
       </c>
       <c r="N21">
-        <v>310.449987</v>
+        <v>309.43946</v>
       </c>
       <c r="O21">
-        <v>93.13499609999998</v>
+        <v>92.83183799999999</v>
       </c>
       <c r="P21">
-        <v>217.3149909</v>
+        <v>216.607622</v>
       </c>
       <c r="Q21">
-        <v>349.4149909</v>
+        <v>348.707622</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1264804903781082</v>
+        <v>0.127229116349273</v>
       </c>
       <c r="T21">
-        <v>0.6202248073610611</v>
+        <v>0.6259798095502545</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.16925920831408</v>
+        <v>16.31079624789837</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1088252930794184</v>
+        <v>0.1085114889525692</v>
       </c>
       <c r="C22">
-        <v>1779.459322173782</v>
+        <v>1766.060096144548</v>
       </c>
       <c r="D22">
-        <v>2130.859322173781</v>
+        <v>2137.550096144548</v>
       </c>
       <c r="E22">
-        <v>55.19999999999999</v>
+        <v>75.29000000000002</v>
       </c>
       <c r="F22">
-        <v>401.8</v>
+        <v>421.89</v>
       </c>
       <c r="G22">
         <v>50.4</v>
@@ -3079,28 +3079,28 @@
         <v>329.65</v>
       </c>
       <c r="M22">
-        <v>20.21054</v>
+        <v>21.221067</v>
       </c>
       <c r="N22">
-        <v>309.43946</v>
+        <v>308.428933</v>
       </c>
       <c r="O22">
-        <v>92.83183799999999</v>
+        <v>92.52867989999999</v>
       </c>
       <c r="P22">
-        <v>216.607622</v>
+        <v>215.9002531</v>
       </c>
       <c r="Q22">
-        <v>348.707622</v>
+        <v>348.0002531</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.127229116349273</v>
+        <v>0.1279966948766699</v>
       </c>
       <c r="T22">
-        <v>0.6259798095502545</v>
+        <v>0.6318805079974021</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.31079624789837</v>
+        <v>15.53409166466512</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1085114889525692</v>
+        <v>0.10819768482572</v>
       </c>
       <c r="C23">
-        <v>1766.060096144549</v>
+        <v>1752.703019742629</v>
       </c>
       <c r="D23">
-        <v>2137.550096144549</v>
+        <v>2144.283019742629</v>
       </c>
       <c r="E23">
-        <v>75.28999999999996</v>
+        <v>95.38</v>
       </c>
       <c r="F23">
-        <v>421.89</v>
+        <v>441.98</v>
       </c>
       <c r="G23">
         <v>50.4</v>
@@ -3161,28 +3161,28 @@
         <v>329.65</v>
       </c>
       <c r="M23">
-        <v>21.221067</v>
+        <v>22.231594</v>
       </c>
       <c r="N23">
-        <v>308.428933</v>
+        <v>307.418406</v>
       </c>
       <c r="O23">
-        <v>92.52867989999999</v>
+        <v>92.2255218</v>
       </c>
       <c r="P23">
-        <v>215.9002531</v>
+        <v>215.1928842</v>
       </c>
       <c r="Q23">
-        <v>348.0002531</v>
+        <v>347.2928842</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1279966948766699</v>
+        <v>0.1287839549047692</v>
       </c>
       <c r="T23">
-        <v>0.6318805079974019</v>
+        <v>0.6379325064047329</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.53409166466512</v>
+        <v>14.82799658899852</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.10819768482572</v>
+        <v>0.1078838806988708</v>
       </c>
       <c r="C24">
-        <v>1752.703019742629</v>
+        <v>1739.38849251927</v>
       </c>
       <c r="D24">
-        <v>2144.283019742629</v>
+        <v>2151.05849251927</v>
       </c>
       <c r="E24">
-        <v>95.38</v>
+        <v>115.47</v>
       </c>
       <c r="F24">
-        <v>441.98</v>
+        <v>462.07</v>
       </c>
       <c r="G24">
         <v>50.4</v>
@@ -3243,28 +3243,28 @@
         <v>329.65</v>
       </c>
       <c r="M24">
-        <v>22.231594</v>
+        <v>23.242121</v>
       </c>
       <c r="N24">
-        <v>307.418406</v>
+        <v>306.407879</v>
       </c>
       <c r="O24">
-        <v>92.2255218</v>
+        <v>91.92236369999999</v>
       </c>
       <c r="P24">
-        <v>215.1928842</v>
+        <v>214.4855153</v>
       </c>
       <c r="Q24">
-        <v>347.2928842</v>
+        <v>346.5855153</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1287839549047692</v>
+        <v>0.1295916632452868</v>
       </c>
       <c r="T24">
-        <v>0.6379325064047329</v>
+        <v>0.6441416995758904</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.82799658899852</v>
+        <v>14.18330108512902</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1078838806988708</v>
+        <v>0.1075700765720216</v>
       </c>
       <c r="C25">
-        <v>1739.38849251927</v>
+        <v>1726.116919091711</v>
       </c>
       <c r="D25">
-        <v>2151.05849251927</v>
+        <v>2157.876919091711</v>
       </c>
       <c r="E25">
-        <v>115.47</v>
+        <v>135.56</v>
       </c>
       <c r="F25">
-        <v>462.07</v>
+        <v>482.16</v>
       </c>
       <c r="G25">
         <v>50.4</v>
@@ -3325,28 +3325,28 @@
         <v>329.65</v>
       </c>
       <c r="M25">
-        <v>23.242121</v>
+        <v>24.252648</v>
       </c>
       <c r="N25">
-        <v>306.407879</v>
+        <v>305.397352</v>
       </c>
       <c r="O25">
-        <v>91.92236369999999</v>
+        <v>91.61920559999999</v>
       </c>
       <c r="P25">
-        <v>214.4855153</v>
+        <v>213.7781464</v>
       </c>
       <c r="Q25">
-        <v>346.5855153</v>
+        <v>345.8781464</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1295916632452868</v>
+        <v>0.1304206270684495</v>
       </c>
       <c r="T25">
-        <v>0.6441416995758904</v>
+        <v>0.6505142925673417</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.18330108512902</v>
+        <v>13.59233020658198</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1075700765720216</v>
+        <v>0.1072562724451724</v>
       </c>
       <c r="C26">
-        <v>1726.116919091711</v>
+        <v>1712.888709223729</v>
       </c>
       <c r="D26">
-        <v>2157.876919091711</v>
+        <v>2164.738709223729</v>
       </c>
       <c r="E26">
-        <v>135.5599999999999</v>
+        <v>155.65</v>
       </c>
       <c r="F26">
-        <v>482.16</v>
+        <v>502.25</v>
       </c>
       <c r="G26">
         <v>50.4</v>
@@ -3407,28 +3407,28 @@
         <v>329.65</v>
       </c>
       <c r="M26">
-        <v>24.252648</v>
+        <v>25.263175</v>
       </c>
       <c r="N26">
-        <v>305.397352</v>
+        <v>304.386825</v>
       </c>
       <c r="O26">
-        <v>91.61920559999999</v>
+        <v>91.3160475</v>
       </c>
       <c r="P26">
-        <v>213.7781464</v>
+        <v>213.0707775</v>
       </c>
       <c r="Q26">
-        <v>345.8781464</v>
+        <v>345.1707775</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1304206270684495</v>
+        <v>0.1312716965935632</v>
       </c>
       <c r="T26">
-        <v>0.6505142925673417</v>
+        <v>0.6570568213718984</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.59233020658198</v>
+        <v>13.0486369983187</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1072562724451724</v>
+        <v>0.1072154683183232</v>
       </c>
       <c r="C27">
-        <v>1712.888709223729</v>
+        <v>1693.694159124339</v>
       </c>
       <c r="D27">
-        <v>2164.738709223729</v>
+        <v>2165.634159124339</v>
       </c>
       <c r="E27">
-        <v>155.65</v>
+        <v>175.74</v>
       </c>
       <c r="F27">
-        <v>502.25</v>
+        <v>522.34</v>
       </c>
       <c r="G27">
         <v>50.4</v>
@@ -3489,45 +3489,45 @@
         <v>329.65</v>
       </c>
       <c r="M27">
-        <v>25.263175</v>
+        <v>27.057212</v>
       </c>
       <c r="N27">
-        <v>304.386825</v>
+        <v>302.592788</v>
       </c>
       <c r="O27">
-        <v>91.3160475</v>
+        <v>90.7778364</v>
       </c>
       <c r="P27">
-        <v>213.0707775</v>
+        <v>211.8149516</v>
       </c>
       <c r="Q27">
-        <v>345.1707775</v>
+        <v>343.9149516</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1312716965935632</v>
+        <v>0.132145767997734</v>
       </c>
       <c r="T27">
-        <v>0.6570568213718984</v>
+        <v>0.6637761752792807</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>13.0486369983187</v>
+        <v>12.18344299479192</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1072154683183232</v>
+        <v>0.106912164191474</v>
       </c>
       <c r="C28">
-        <v>1693.694159124339</v>
+        <v>1680.283483541478</v>
       </c>
       <c r="D28">
-        <v>2165.634159124339</v>
+        <v>2172.313483541478</v>
       </c>
       <c r="E28">
-        <v>175.74</v>
+        <v>195.83</v>
       </c>
       <c r="F28">
-        <v>522.34</v>
+        <v>542.4300000000001</v>
       </c>
       <c r="G28">
         <v>50.4</v>
@@ -3571,28 +3571,28 @@
         <v>329.65</v>
       </c>
       <c r="M28">
-        <v>27.057212</v>
+        <v>28.097874</v>
       </c>
       <c r="N28">
-        <v>302.592788</v>
+        <v>301.552126</v>
       </c>
       <c r="O28">
-        <v>90.7778364</v>
+        <v>90.4656378</v>
       </c>
       <c r="P28">
-        <v>211.8149516</v>
+        <v>211.0864882</v>
       </c>
       <c r="Q28">
-        <v>343.9149516</v>
+        <v>343.1864882</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.132145767997734</v>
+        <v>0.133043786563663</v>
       </c>
       <c r="T28">
-        <v>0.6637761752792807</v>
+        <v>0.6706796210745367</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.18344299479192</v>
+        <v>11.73220436535519</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.106912164191474</v>
+        <v>0.1066088600646248</v>
       </c>
       <c r="C29">
-        <v>1680.283483541478</v>
+        <v>1666.914136636691</v>
       </c>
       <c r="D29">
-        <v>2172.313483541478</v>
+        <v>2179.034136636691</v>
       </c>
       <c r="E29">
-        <v>195.83</v>
+        <v>215.9200000000001</v>
       </c>
       <c r="F29">
-        <v>542.4300000000001</v>
+        <v>562.5200000000001</v>
       </c>
       <c r="G29">
         <v>50.4</v>
@@ -3653,28 +3653,28 @@
         <v>329.65</v>
       </c>
       <c r="M29">
-        <v>28.097874</v>
+        <v>29.13853600000001</v>
       </c>
       <c r="N29">
-        <v>301.552126</v>
+        <v>300.511464</v>
       </c>
       <c r="O29">
-        <v>90.4656378</v>
+        <v>90.15343919999999</v>
       </c>
       <c r="P29">
-        <v>211.0864882</v>
+        <v>210.3580248</v>
       </c>
       <c r="Q29">
-        <v>343.1864882</v>
+        <v>342.4580248</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.133043786563663</v>
+        <v>0.1339667500897566</v>
       </c>
       <c r="T29">
-        <v>0.6706796210745367</v>
+        <v>0.6777748292529941</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.73220436535519</v>
+        <v>11.3131970665925</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1066088600646248</v>
+        <v>0.1063055559377755</v>
       </c>
       <c r="C30">
-        <v>1666.914136636691</v>
+        <v>1653.586503185506</v>
       </c>
       <c r="D30">
-        <v>2179.034136636691</v>
+        <v>2185.796503185506</v>
       </c>
       <c r="E30">
-        <v>215.9200000000001</v>
+        <v>236.0100000000001</v>
       </c>
       <c r="F30">
-        <v>562.5200000000001</v>
+        <v>582.6100000000001</v>
       </c>
       <c r="G30">
         <v>50.4</v>
@@ -3735,28 +3735,28 @@
         <v>329.65</v>
       </c>
       <c r="M30">
-        <v>29.13853600000001</v>
+        <v>30.17919800000001</v>
       </c>
       <c r="N30">
-        <v>300.511464</v>
+        <v>299.470802</v>
       </c>
       <c r="O30">
-        <v>90.15343919999999</v>
+        <v>89.84124059999999</v>
       </c>
       <c r="P30">
-        <v>210.3580248</v>
+        <v>209.6295614</v>
       </c>
       <c r="Q30">
-        <v>342.4580248</v>
+        <v>341.7295614</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1339667500897566</v>
+        <v>0.1349157125884163</v>
       </c>
       <c r="T30">
-        <v>0.6777748292529941</v>
+        <v>0.6850699024505632</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.3131970665925</v>
+        <v>10.9230868229169</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1063055559377755</v>
+        <v>0.1060022518109263</v>
       </c>
       <c r="C31">
-        <v>1653.586503185506</v>
+        <v>1640.300972754734</v>
       </c>
       <c r="D31">
-        <v>2185.796503185506</v>
+        <v>2192.600972754733</v>
       </c>
       <c r="E31">
-        <v>236.01</v>
+        <v>256.0999999999999</v>
       </c>
       <c r="F31">
-        <v>582.61</v>
+        <v>602.6999999999999</v>
       </c>
       <c r="G31">
         <v>50.4</v>
@@ -3817,28 +3817,28 @@
         <v>329.65</v>
       </c>
       <c r="M31">
-        <v>30.179198</v>
+        <v>31.21986</v>
       </c>
       <c r="N31">
-        <v>299.470802</v>
+        <v>298.43014</v>
       </c>
       <c r="O31">
-        <v>89.84124059999999</v>
+        <v>89.52904199999999</v>
       </c>
       <c r="P31">
-        <v>209.6295614</v>
+        <v>208.901098</v>
       </c>
       <c r="Q31">
-        <v>341.7295614</v>
+        <v>341.001098</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1349157125884163</v>
+        <v>0.1358917883013234</v>
       </c>
       <c r="T31">
-        <v>0.6850699024505632</v>
+        <v>0.6925734063109199</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.9230868229169</v>
+        <v>10.55898392881967</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1060022518109263</v>
+        <v>0.1056989476840771</v>
       </c>
       <c r="C32">
-        <v>1640.300972754734</v>
+        <v>1627.057939777284</v>
       </c>
       <c r="D32">
-        <v>2192.600972754733</v>
+        <v>2199.447939777284</v>
       </c>
       <c r="E32">
-        <v>256.0999999999999</v>
+        <v>276.1899999999999</v>
       </c>
       <c r="F32">
-        <v>602.6999999999999</v>
+        <v>622.79</v>
       </c>
       <c r="G32">
         <v>50.4</v>
@@ -3899,28 +3899,28 @@
         <v>329.65</v>
       </c>
       <c r="M32">
-        <v>31.21986</v>
+        <v>32.26052199999999</v>
       </c>
       <c r="N32">
-        <v>298.43014</v>
+        <v>297.389478</v>
       </c>
       <c r="O32">
-        <v>89.52904199999999</v>
+        <v>89.2168434</v>
       </c>
       <c r="P32">
-        <v>208.901098</v>
+        <v>208.1726346</v>
       </c>
       <c r="Q32">
-        <v>341.001098</v>
+        <v>340.2726345999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1358917883013234</v>
+        <v>0.1368961560638799</v>
       </c>
       <c r="T32">
-        <v>0.6925734063109199</v>
+        <v>0.700294403036794</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.55898392881967</v>
+        <v>10.21837154401904</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1056989476840771</v>
+        <v>0.1053956435572279</v>
       </c>
       <c r="C33">
-        <v>1627.057939777284</v>
+        <v>1613.857803628375</v>
       </c>
       <c r="D33">
-        <v>2199.447939777284</v>
+        <v>2206.337803628375</v>
       </c>
       <c r="E33">
-        <v>276.1899999999999</v>
+        <v>296.28</v>
       </c>
       <c r="F33">
-        <v>622.79</v>
+        <v>642.88</v>
       </c>
       <c r="G33">
         <v>50.4</v>
@@ -3981,28 +3981,28 @@
         <v>329.65</v>
       </c>
       <c r="M33">
-        <v>32.26052199999999</v>
+        <v>33.301184</v>
       </c>
       <c r="N33">
-        <v>297.389478</v>
+        <v>296.348816</v>
       </c>
       <c r="O33">
-        <v>89.2168434</v>
+        <v>88.9046448</v>
       </c>
       <c r="P33">
-        <v>208.1726346</v>
+        <v>207.4441712</v>
       </c>
       <c r="Q33">
-        <v>340.2726345999999</v>
+        <v>339.5441712</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1368961560638799</v>
+        <v>0.1379300640547469</v>
       </c>
       <c r="T33">
-        <v>0.700294403036794</v>
+        <v>0.7082424879016646</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.21837154401904</v>
+        <v>9.899047433268439</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1053956435572279</v>
+        <v>0.1054850394303787</v>
       </c>
       <c r="C34">
-        <v>1613.857803628375</v>
+        <v>1591.73260257994</v>
       </c>
       <c r="D34">
-        <v>2206.337803628375</v>
+        <v>2204.30260257994</v>
       </c>
       <c r="E34">
-        <v>296.28</v>
+        <v>316.37</v>
       </c>
       <c r="F34">
-        <v>642.88</v>
+        <v>662.97</v>
       </c>
       <c r="G34">
         <v>50.4</v>
@@ -4063,45 +4063,45 @@
         <v>329.65</v>
       </c>
       <c r="M34">
-        <v>33.301184</v>
+        <v>35.468895</v>
       </c>
       <c r="N34">
-        <v>296.348816</v>
+        <v>294.181105</v>
       </c>
       <c r="O34">
-        <v>88.9046448</v>
+        <v>88.25433149999999</v>
       </c>
       <c r="P34">
-        <v>207.4441712</v>
+        <v>205.9267735</v>
       </c>
       <c r="Q34">
-        <v>339.5441712</v>
+        <v>338.0267735</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1379300640547469</v>
+        <v>0.1389948349707145</v>
       </c>
       <c r="T34">
-        <v>0.7082424879016646</v>
+        <v>0.7164278290311583</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>9.899047433268439</v>
+        <v>9.294058921204057</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1054850394303787</v>
+        <v>0.1051936353035295</v>
       </c>
       <c r="C35">
-        <v>1591.73260257994</v>
+        <v>1578.290626647996</v>
       </c>
       <c r="D35">
-        <v>2204.30260257994</v>
+        <v>2210.950626647996</v>
       </c>
       <c r="E35">
-        <v>316.37</v>
+        <v>336.46</v>
       </c>
       <c r="F35">
-        <v>662.97</v>
+        <v>683.0600000000001</v>
       </c>
       <c r="G35">
         <v>50.4</v>
@@ -4145,28 +4145,28 @@
         <v>329.65</v>
       </c>
       <c r="M35">
-        <v>35.468895</v>
+        <v>36.54371</v>
       </c>
       <c r="N35">
-        <v>294.181105</v>
+        <v>293.1062899999999</v>
       </c>
       <c r="O35">
-        <v>88.25433149999999</v>
+        <v>87.93188699999997</v>
       </c>
       <c r="P35">
-        <v>205.9267735</v>
+        <v>205.174403</v>
       </c>
       <c r="Q35">
-        <v>338.0267735</v>
+        <v>337.274403</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1389948349707145</v>
+        <v>0.1400918716720144</v>
       </c>
       <c r="T35">
-        <v>0.7164278290311583</v>
+        <v>0.7248612108009395</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.294058921204057</v>
+        <v>9.020704247050995</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1051936353035295</v>
+        <v>0.1049022311766803</v>
       </c>
       <c r="C36">
-        <v>1578.290626647996</v>
+        <v>1564.888871981434</v>
       </c>
       <c r="D36">
-        <v>2210.950626647996</v>
+        <v>2217.638871981434</v>
       </c>
       <c r="E36">
-        <v>336.46</v>
+        <v>356.5500000000001</v>
       </c>
       <c r="F36">
-        <v>683.0600000000001</v>
+        <v>703.1500000000001</v>
       </c>
       <c r="G36">
         <v>50.4</v>
@@ -4227,28 +4227,28 @@
         <v>329.65</v>
       </c>
       <c r="M36">
-        <v>36.54371</v>
+        <v>37.61852500000001</v>
       </c>
       <c r="N36">
-        <v>293.1062899999999</v>
+        <v>292.031475</v>
       </c>
       <c r="O36">
-        <v>87.93188699999997</v>
+        <v>87.6094425</v>
       </c>
       <c r="P36">
-        <v>205.174403</v>
+        <v>204.4220325</v>
       </c>
       <c r="Q36">
-        <v>337.274403</v>
+        <v>336.5220325</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1400918716720144</v>
+        <v>0.141222663348739</v>
       </c>
       <c r="T36">
-        <v>0.7248612108009395</v>
+        <v>0.7335540812405601</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.020704247050995</v>
+        <v>8.762969839992397</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1049022311766803</v>
+        <v>0.1046108270498311</v>
       </c>
       <c r="C37">
-        <v>1564.888871981434</v>
+        <v>1551.527704702306</v>
       </c>
       <c r="D37">
-        <v>2217.638871981434</v>
+        <v>2224.367704702307</v>
       </c>
       <c r="E37">
-        <v>356.5500000000001</v>
+        <v>376.6400000000001</v>
       </c>
       <c r="F37">
-        <v>703.1500000000001</v>
+        <v>723.2400000000001</v>
       </c>
       <c r="G37">
         <v>50.4</v>
@@ -4309,28 +4309,28 @@
         <v>329.65</v>
       </c>
       <c r="M37">
-        <v>37.61852500000001</v>
+        <v>38.69334000000001</v>
       </c>
       <c r="N37">
-        <v>292.031475</v>
+        <v>290.9566599999999</v>
       </c>
       <c r="O37">
-        <v>87.6094425</v>
+        <v>87.28699799999998</v>
       </c>
       <c r="P37">
-        <v>204.4220325</v>
+        <v>203.669662</v>
       </c>
       <c r="Q37">
-        <v>336.5220325</v>
+        <v>335.7696619999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.141222663348739</v>
+        <v>0.1423887922653611</v>
       </c>
       <c r="T37">
-        <v>0.7335540812405601</v>
+        <v>0.7425186038814189</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.762969839992397</v>
+        <v>8.519554011103718</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1046108270498311</v>
+        <v>0.1043194229229819</v>
       </c>
       <c r="C38">
-        <v>1551.527704702307</v>
+        <v>1538.207495389792</v>
       </c>
       <c r="D38">
-        <v>2224.367704702307</v>
+        <v>2231.137495389792</v>
       </c>
       <c r="E38">
-        <v>376.64</v>
+        <v>396.73</v>
       </c>
       <c r="F38">
-        <v>723.24</v>
+        <v>743.33</v>
       </c>
       <c r="G38">
         <v>50.4</v>
@@ -4391,28 +4391,28 @@
         <v>329.65</v>
       </c>
       <c r="M38">
-        <v>38.69334</v>
+        <v>39.768155</v>
       </c>
       <c r="N38">
-        <v>290.95666</v>
+        <v>289.881845</v>
       </c>
       <c r="O38">
-        <v>87.286998</v>
+        <v>86.96455349999999</v>
       </c>
       <c r="P38">
-        <v>203.669662</v>
+        <v>202.9172915</v>
       </c>
       <c r="Q38">
-        <v>335.769662</v>
+        <v>335.0172915</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1423887922653611</v>
+        <v>0.1435919411475903</v>
       </c>
       <c r="T38">
-        <v>0.7425186038814189</v>
+        <v>0.7517677145426224</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.51955401110372</v>
+        <v>8.289295794587403</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1043194229229819</v>
+        <v>0.1040280187961327</v>
       </c>
       <c r="C39">
-        <v>1538.207495389792</v>
+        <v>1524.928619148222</v>
       </c>
       <c r="D39">
-        <v>2231.137495389792</v>
+        <v>2237.948619148221</v>
       </c>
       <c r="E39">
-        <v>396.73</v>
+        <v>416.8199999999999</v>
       </c>
       <c r="F39">
-        <v>743.33</v>
+        <v>763.42</v>
       </c>
       <c r="G39">
         <v>50.4</v>
@@ -4473,28 +4473,28 @@
         <v>329.65</v>
       </c>
       <c r="M39">
-        <v>39.768155</v>
+        <v>40.84296999999999</v>
       </c>
       <c r="N39">
-        <v>289.881845</v>
+        <v>288.80703</v>
       </c>
       <c r="O39">
-        <v>86.96455349999999</v>
+        <v>86.64210899999999</v>
       </c>
       <c r="P39">
-        <v>202.9172915</v>
+        <v>202.164921</v>
       </c>
       <c r="Q39">
-        <v>335.0172915</v>
+        <v>334.264921</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1435919411475903</v>
+        <v>0.144833901284085</v>
       </c>
       <c r="T39">
-        <v>0.7517677145426224</v>
+        <v>0.7613151836122518</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.289295794587403</v>
+        <v>8.071156431571946</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1040280187961327</v>
+        <v>0.1037366146692835</v>
       </c>
       <c r="C40">
-        <v>1524.928619148222</v>
+        <v>1511.691455676363</v>
       </c>
       <c r="D40">
-        <v>2237.948619148221</v>
+        <v>2244.801455676363</v>
       </c>
       <c r="E40">
-        <v>416.8199999999999</v>
+        <v>436.91</v>
       </c>
       <c r="F40">
-        <v>763.42</v>
+        <v>783.51</v>
       </c>
       <c r="G40">
         <v>50.4</v>
@@ -4555,28 +4555,28 @@
         <v>329.65</v>
       </c>
       <c r="M40">
-        <v>40.84296999999999</v>
+        <v>41.917785</v>
       </c>
       <c r="N40">
-        <v>288.80703</v>
+        <v>287.732215</v>
       </c>
       <c r="O40">
-        <v>86.64210899999999</v>
+        <v>86.3196645</v>
       </c>
       <c r="P40">
-        <v>202.164921</v>
+        <v>201.4125505</v>
       </c>
       <c r="Q40">
-        <v>334.264921</v>
+        <v>333.5125505</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.144833901284085</v>
+        <v>0.1461165814250549</v>
       </c>
       <c r="T40">
-        <v>0.7613151836122518</v>
+        <v>0.771175684454656</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.071156431571946</v>
+        <v>7.864203702557279</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1037366146692835</v>
+        <v>0.1034452105424343</v>
       </c>
       <c r="C41">
-        <v>1511.691455676363</v>
+        <v>1498.496389337983</v>
       </c>
       <c r="D41">
-        <v>2244.801455676363</v>
+        <v>2251.696389337983</v>
       </c>
       <c r="E41">
-        <v>436.91</v>
+        <v>457</v>
       </c>
       <c r="F41">
-        <v>783.51</v>
+        <v>803.6</v>
       </c>
       <c r="G41">
         <v>50.4</v>
@@ -4637,28 +4637,28 @@
         <v>329.65</v>
       </c>
       <c r="M41">
-        <v>41.917785</v>
+        <v>42.9926</v>
       </c>
       <c r="N41">
-        <v>287.732215</v>
+        <v>286.6574</v>
       </c>
       <c r="O41">
-        <v>86.3196645</v>
+        <v>85.99722</v>
       </c>
       <c r="P41">
-        <v>201.4125505</v>
+        <v>200.66018</v>
       </c>
       <c r="Q41">
-        <v>333.5125505</v>
+        <v>332.76018</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1461165814250549</v>
+        <v>0.1474420175707238</v>
       </c>
       <c r="T41">
-        <v>0.771175684454656</v>
+        <v>0.7813648686584738</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.864203702557279</v>
+        <v>7.667598609993347</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1034452105424343</v>
+        <v>0.1033834064155851</v>
       </c>
       <c r="C42">
-        <v>1498.496389337983</v>
+        <v>1479.874188968734</v>
       </c>
       <c r="D42">
-        <v>2251.696389337983</v>
+        <v>2253.164188968734</v>
       </c>
       <c r="E42">
-        <v>457</v>
+        <v>477.09</v>
       </c>
       <c r="F42">
-        <v>803.6</v>
+        <v>823.6900000000001</v>
       </c>
       <c r="G42">
         <v>50.4</v>
@@ -4719,45 +4719,45 @@
         <v>329.65</v>
       </c>
       <c r="M42">
-        <v>42.9926</v>
+        <v>44.726367</v>
       </c>
       <c r="N42">
-        <v>286.6574</v>
+        <v>284.923633</v>
       </c>
       <c r="O42">
-        <v>85.99722</v>
+        <v>85.4770899</v>
       </c>
       <c r="P42">
-        <v>200.66018</v>
+        <v>199.4465431</v>
       </c>
       <c r="Q42">
-        <v>332.76018</v>
+        <v>331.5465431</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1474420175707238</v>
+        <v>0.1488123837552289</v>
       </c>
       <c r="T42">
-        <v>0.7813648686584738</v>
+        <v>0.791899448936997</v>
       </c>
       <c r="U42">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>7.667598609993347</v>
+        <v>7.370372827285524</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1033834064155851</v>
+        <v>0.1030976022887359</v>
       </c>
       <c r="C43">
-        <v>1479.874188968734</v>
+        <v>1466.596774044996</v>
       </c>
       <c r="D43">
-        <v>2253.164188968734</v>
+        <v>2259.976774044996</v>
       </c>
       <c r="E43">
-        <v>477.09</v>
+        <v>497.1800000000001</v>
       </c>
       <c r="F43">
-        <v>823.6900000000001</v>
+        <v>843.7800000000001</v>
       </c>
       <c r="G43">
         <v>50.4</v>
@@ -4801,28 +4801,28 @@
         <v>329.65</v>
       </c>
       <c r="M43">
-        <v>44.726367</v>
+        <v>45.81725400000001</v>
       </c>
       <c r="N43">
-        <v>284.923633</v>
+        <v>283.832746</v>
       </c>
       <c r="O43">
-        <v>85.4770899</v>
+        <v>85.14982379999999</v>
       </c>
       <c r="P43">
-        <v>199.4465431</v>
+        <v>198.6829222</v>
       </c>
       <c r="Q43">
-        <v>331.5465431</v>
+        <v>330.7829222</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1488123837552289</v>
+        <v>0.1502300039460963</v>
       </c>
       <c r="T43">
-        <v>0.791899448936997</v>
+        <v>0.8027972906044349</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.370372827285524</v>
+        <v>7.194887759969202</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1030976022887359</v>
+        <v>0.1028117981618867</v>
       </c>
       <c r="C44">
-        <v>1466.596774044996</v>
+        <v>1453.360680627064</v>
       </c>
       <c r="D44">
-        <v>2259.976774044996</v>
+        <v>2266.830680627064</v>
       </c>
       <c r="E44">
-        <v>497.1799999999999</v>
+        <v>517.27</v>
       </c>
       <c r="F44">
-        <v>843.78</v>
+        <v>863.87</v>
       </c>
       <c r="G44">
         <v>50.4</v>
@@ -4883,28 +4883,28 @@
         <v>329.65</v>
       </c>
       <c r="M44">
-        <v>45.817254</v>
+        <v>46.908141</v>
       </c>
       <c r="N44">
-        <v>283.832746</v>
+        <v>282.741859</v>
       </c>
       <c r="O44">
-        <v>85.14982379999999</v>
+        <v>84.82255769999999</v>
       </c>
       <c r="P44">
-        <v>198.6829222</v>
+        <v>197.9193013</v>
       </c>
       <c r="Q44">
-        <v>330.7829222</v>
+        <v>330.0193012999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1502300039460963</v>
+        <v>0.1516973651962924</v>
       </c>
       <c r="T44">
-        <v>0.8027972906044348</v>
+        <v>0.8140775126812566</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.194887759969203</v>
+        <v>7.027564788807128</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1028117981618867</v>
+        <v>0.1025259940350374</v>
       </c>
       <c r="C45">
-        <v>1453.360680627064</v>
+        <v>1440.166285809873</v>
       </c>
       <c r="D45">
-        <v>2266.830680627064</v>
+        <v>2273.726285809873</v>
       </c>
       <c r="E45">
-        <v>517.27</v>
+        <v>537.36</v>
       </c>
       <c r="F45">
-        <v>863.87</v>
+        <v>883.96</v>
       </c>
       <c r="G45">
         <v>50.4</v>
@@ -4965,28 +4965,28 @@
         <v>329.65</v>
       </c>
       <c r="M45">
-        <v>46.908141</v>
+        <v>47.999028</v>
       </c>
       <c r="N45">
-        <v>282.741859</v>
+        <v>281.650972</v>
       </c>
       <c r="O45">
-        <v>84.82255769999999</v>
+        <v>84.49529159999999</v>
       </c>
       <c r="P45">
-        <v>197.9193013</v>
+        <v>197.1556804</v>
       </c>
       <c r="Q45">
-        <v>330.0193012999999</v>
+        <v>329.2556804</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1516973651962924</v>
+        <v>0.153217132205424</v>
       </c>
       <c r="T45">
-        <v>0.8140775126812566</v>
+        <v>0.8257605998322505</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.027564788807128</v>
+        <v>6.867847407243329</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1025259940350374</v>
+        <v>0.1022401899081882</v>
       </c>
       <c r="C46">
-        <v>1440.166285809873</v>
+        <v>1427.013971290788</v>
       </c>
       <c r="D46">
-        <v>2273.726285809873</v>
+        <v>2280.663971290788</v>
       </c>
       <c r="E46">
-        <v>537.36</v>
+        <v>557.45</v>
       </c>
       <c r="F46">
-        <v>883.96</v>
+        <v>904.0500000000001</v>
       </c>
       <c r="G46">
         <v>50.4</v>
@@ -5047,28 +5047,28 @@
         <v>329.65</v>
       </c>
       <c r="M46">
-        <v>47.999028</v>
+        <v>49.089915</v>
       </c>
       <c r="N46">
-        <v>281.650972</v>
+        <v>280.560085</v>
       </c>
       <c r="O46">
-        <v>84.49529159999999</v>
+        <v>84.16802549999998</v>
       </c>
       <c r="P46">
-        <v>197.1556804</v>
+        <v>196.3920595</v>
       </c>
       <c r="Q46">
-        <v>329.2556804</v>
+        <v>328.4920595</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.153217132205424</v>
+        <v>0.1547921634694332</v>
       </c>
       <c r="T46">
-        <v>0.8257605998322505</v>
+        <v>0.837868526516008</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.867847407243329</v>
+        <v>6.715228575971254</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1022401899081882</v>
+        <v>0.101954385781339</v>
       </c>
       <c r="C47">
-        <v>1427.013971290788</v>
+        <v>1413.904123440034</v>
       </c>
       <c r="D47">
-        <v>2280.663971290788</v>
+        <v>2287.644123440034</v>
       </c>
       <c r="E47">
-        <v>557.45</v>
+        <v>577.54</v>
       </c>
       <c r="F47">
-        <v>904.0500000000001</v>
+        <v>924.14</v>
       </c>
       <c r="G47">
         <v>50.4</v>
@@ -5129,28 +5129,28 @@
         <v>329.65</v>
       </c>
       <c r="M47">
-        <v>49.089915</v>
+        <v>50.180802</v>
       </c>
       <c r="N47">
-        <v>280.560085</v>
+        <v>279.469198</v>
       </c>
       <c r="O47">
-        <v>84.16802549999998</v>
+        <v>83.8407594</v>
       </c>
       <c r="P47">
-        <v>196.3920595</v>
+        <v>195.6284386</v>
       </c>
       <c r="Q47">
-        <v>328.4920595</v>
+        <v>327.7284386</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1547921634694332</v>
+        <v>0.1564255292247019</v>
       </c>
       <c r="T47">
-        <v>0.837868526516008</v>
+        <v>0.8504248949287933</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.715228575971254</v>
+        <v>6.569245346058837</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.101954385781339</v>
+        <v>0.1016685816544898</v>
       </c>
       <c r="C48">
-        <v>1413.904123440034</v>
+        <v>1400.83713337242</v>
       </c>
       <c r="D48">
-        <v>2287.644123440034</v>
+        <v>2294.66713337242</v>
       </c>
       <c r="E48">
-        <v>577.54</v>
+        <v>597.63</v>
       </c>
       <c r="F48">
-        <v>924.14</v>
+        <v>944.23</v>
       </c>
       <c r="G48">
         <v>50.4</v>
@@ -5211,28 +5211,28 @@
         <v>329.65</v>
       </c>
       <c r="M48">
-        <v>50.180802</v>
+        <v>51.271689</v>
       </c>
       <c r="N48">
-        <v>279.469198</v>
+        <v>278.378311</v>
       </c>
       <c r="O48">
-        <v>83.8407594</v>
+        <v>83.51349329999999</v>
       </c>
       <c r="P48">
-        <v>195.6284386</v>
+        <v>194.8648177</v>
       </c>
       <c r="Q48">
-        <v>327.7284386</v>
+        <v>326.9648177</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1564255292247019</v>
+        <v>0.1581205314235657</v>
       </c>
       <c r="T48">
-        <v>0.8504248949287933</v>
+        <v>0.8634550885647027</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.569245346058837</v>
+        <v>6.429474168483117</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1016685816544898</v>
+        <v>0.1013827775276406</v>
       </c>
       <c r="C49">
-        <v>1400.83713337242</v>
+        <v>1387.8133970204</v>
       </c>
       <c r="D49">
-        <v>2294.66713337242</v>
+        <v>2301.7333970204</v>
       </c>
       <c r="E49">
-        <v>597.63</v>
+        <v>617.72</v>
       </c>
       <c r="F49">
-        <v>944.23</v>
+        <v>964.3200000000001</v>
       </c>
       <c r="G49">
         <v>50.4</v>
@@ -5293,28 +5293,28 @@
         <v>329.65</v>
       </c>
       <c r="M49">
-        <v>51.271689</v>
+        <v>52.362576</v>
       </c>
       <c r="N49">
-        <v>278.378311</v>
+        <v>277.287424</v>
       </c>
       <c r="O49">
-        <v>83.51349329999999</v>
+        <v>83.18622719999999</v>
       </c>
       <c r="P49">
-        <v>194.8648177</v>
+        <v>194.1011968</v>
       </c>
       <c r="Q49">
-        <v>326.9648177</v>
+        <v>326.2011968</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1581205314235657</v>
+        <v>0.1598807260146935</v>
       </c>
       <c r="T49">
-        <v>0.8634550885647027</v>
+        <v>0.8769864434943008</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.429474168483117</v>
+        <v>6.295526789973052</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1013827775276406</v>
+        <v>0.1010969734007914</v>
       </c>
       <c r="C50">
-        <v>1387.813397020401</v>
+        <v>1374.833315208475</v>
       </c>
       <c r="D50">
-        <v>2301.7333970204</v>
+        <v>2308.843315208474</v>
       </c>
       <c r="E50">
-        <v>617.7199999999999</v>
+        <v>637.8099999999999</v>
       </c>
       <c r="F50">
-        <v>964.3199999999999</v>
+        <v>984.41</v>
       </c>
       <c r="G50">
         <v>50.4</v>
@@ -5375,28 +5375,28 @@
         <v>329.65</v>
       </c>
       <c r="M50">
-        <v>52.362576</v>
+        <v>53.453463</v>
       </c>
       <c r="N50">
-        <v>277.287424</v>
+        <v>276.196537</v>
       </c>
       <c r="O50">
-        <v>83.18622719999999</v>
+        <v>82.85896109999999</v>
       </c>
       <c r="P50">
-        <v>194.1011968</v>
+        <v>193.3375759</v>
       </c>
       <c r="Q50">
-        <v>326.2011968</v>
+        <v>325.4375759</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1598807260146935</v>
+        <v>0.161709947844689</v>
       </c>
       <c r="T50">
-        <v>0.8769864434943008</v>
+        <v>0.8910484397936871</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.295526789973053</v>
+        <v>6.167046651402173</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1010969734007914</v>
+        <v>0.1011611692739422</v>
       </c>
       <c r="C51">
-        <v>1374.833315208475</v>
+        <v>1353.142499114736</v>
       </c>
       <c r="D51">
-        <v>2308.843315208474</v>
+        <v>2307.242499114736</v>
       </c>
       <c r="E51">
-        <v>637.8099999999999</v>
+        <v>657.9</v>
       </c>
       <c r="F51">
-        <v>984.41</v>
+        <v>1004.5</v>
       </c>
       <c r="G51">
         <v>50.4</v>
@@ -5457,45 +5457,45 @@
         <v>329.65</v>
       </c>
       <c r="M51">
-        <v>53.453463</v>
+        <v>55.54885</v>
       </c>
       <c r="N51">
-        <v>276.196537</v>
+        <v>274.10115</v>
       </c>
       <c r="O51">
-        <v>82.85896109999999</v>
+        <v>82.23034499999999</v>
       </c>
       <c r="P51">
-        <v>193.3375759</v>
+        <v>191.870805</v>
       </c>
       <c r="Q51">
-        <v>325.4375759</v>
+        <v>323.9708049999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.161709947844689</v>
+        <v>0.1636123385478844</v>
       </c>
       <c r="T51">
-        <v>0.8910484397936871</v>
+        <v>0.905672915945049</v>
       </c>
       <c r="U51">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>6.167046651402173</v>
+        <v>5.934416284045484</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1011611692739422</v>
+        <v>0.100882365147093</v>
       </c>
       <c r="C52">
-        <v>1353.142499114736</v>
+        <v>1340.021042843159</v>
       </c>
       <c r="D52">
-        <v>2307.242499114736</v>
+        <v>2314.211042843159</v>
       </c>
       <c r="E52">
-        <v>657.9</v>
+        <v>677.9899999999999</v>
       </c>
       <c r="F52">
-        <v>1004.5</v>
+        <v>1024.59</v>
       </c>
       <c r="G52">
         <v>50.4</v>
@@ -5539,28 +5539,28 @@
         <v>329.65</v>
       </c>
       <c r="M52">
-        <v>55.54885</v>
+        <v>56.659827</v>
       </c>
       <c r="N52">
-        <v>274.10115</v>
+        <v>272.990173</v>
       </c>
       <c r="O52">
-        <v>82.23034499999999</v>
+        <v>81.89705189999999</v>
       </c>
       <c r="P52">
-        <v>191.870805</v>
+        <v>191.0931211</v>
       </c>
       <c r="Q52">
-        <v>323.9708049999999</v>
+        <v>323.1931211</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1636123385478844</v>
+        <v>0.1655923778512102</v>
       </c>
       <c r="T52">
-        <v>0.905672915945049</v>
+        <v>0.920894309490344</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.934416284045484</v>
+        <v>5.818055180436748</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.100882365147093</v>
+        <v>0.1006035610202438</v>
       </c>
       <c r="C53">
-        <v>1340.021042843159</v>
+        <v>1326.941808152697</v>
       </c>
       <c r="D53">
-        <v>2314.211042843159</v>
+        <v>2321.221808152697</v>
       </c>
       <c r="E53">
-        <v>677.9899999999999</v>
+        <v>698.08</v>
       </c>
       <c r="F53">
-        <v>1024.59</v>
+        <v>1044.68</v>
       </c>
       <c r="G53">
         <v>50.4</v>
@@ -5621,28 +5621,28 @@
         <v>329.65</v>
       </c>
       <c r="M53">
-        <v>56.659827</v>
+        <v>57.77080400000001</v>
       </c>
       <c r="N53">
-        <v>272.990173</v>
+        <v>271.879196</v>
       </c>
       <c r="O53">
-        <v>81.89705189999999</v>
+        <v>81.56375879999999</v>
       </c>
       <c r="P53">
-        <v>191.0931211</v>
+        <v>190.3154372</v>
       </c>
       <c r="Q53">
-        <v>323.1931211</v>
+        <v>322.4154372</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1655923778512102</v>
+        <v>0.1676549187921745</v>
       </c>
       <c r="T53">
-        <v>0.920894309490344</v>
+        <v>0.9367499277666929</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.818055180436748</v>
+        <v>5.706169503889888</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1006035610202438</v>
+        <v>0.1003247568933946</v>
       </c>
       <c r="C54">
-        <v>1326.941808152697</v>
+        <v>1313.905179932686</v>
       </c>
       <c r="D54">
-        <v>2321.221808152697</v>
+        <v>2328.275179932686</v>
       </c>
       <c r="E54">
-        <v>698.08</v>
+        <v>718.17</v>
       </c>
       <c r="F54">
-        <v>1044.68</v>
+        <v>1064.77</v>
       </c>
       <c r="G54">
         <v>50.4</v>
@@ -5703,28 +5703,28 @@
         <v>329.65</v>
       </c>
       <c r="M54">
-        <v>57.77080400000001</v>
+        <v>58.881781</v>
       </c>
       <c r="N54">
-        <v>271.879196</v>
+        <v>270.768219</v>
       </c>
       <c r="O54">
-        <v>81.56375879999999</v>
+        <v>81.2304657</v>
       </c>
       <c r="P54">
-        <v>190.3154372</v>
+        <v>189.5377533</v>
       </c>
       <c r="Q54">
-        <v>322.4154372</v>
+        <v>321.6377533</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1676549187921745</v>
+        <v>0.1698052274327544</v>
       </c>
       <c r="T54">
-        <v>0.9367499277666929</v>
+        <v>0.9532802532037374</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.706169503889888</v>
+        <v>5.598505928344796</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1003247568933946</v>
+        <v>0.1000459527665454</v>
       </c>
       <c r="C55">
-        <v>1313.905179932686</v>
+        <v>1300.911547764893</v>
       </c>
       <c r="D55">
-        <v>2328.275179932686</v>
+        <v>2335.371547764893</v>
       </c>
       <c r="E55">
-        <v>718.17</v>
+        <v>738.2600000000001</v>
       </c>
       <c r="F55">
-        <v>1064.77</v>
+        <v>1084.86</v>
       </c>
       <c r="G55">
         <v>50.4</v>
@@ -5785,28 +5785,28 @@
         <v>329.65</v>
       </c>
       <c r="M55">
-        <v>58.881781</v>
+        <v>59.99275800000001</v>
       </c>
       <c r="N55">
-        <v>270.768219</v>
+        <v>269.657242</v>
       </c>
       <c r="O55">
-        <v>81.2304657</v>
+        <v>80.89717259999999</v>
       </c>
       <c r="P55">
-        <v>189.5377533</v>
+        <v>188.7600694</v>
       </c>
       <c r="Q55">
-        <v>321.6377533</v>
+        <v>320.8600694</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1698052274327544</v>
+        <v>0.1720490277533595</v>
       </c>
       <c r="T55">
-        <v>0.9532802532037374</v>
+        <v>0.9705292884423926</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.598505928344796</v>
+        <v>5.494829892634707</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1000459527665454</v>
+        <v>0.09976714863969616</v>
       </c>
       <c r="C56">
-        <v>1300.911547764893</v>
+        <v>1287.961305995244</v>
       </c>
       <c r="D56">
-        <v>2335.371547764893</v>
+        <v>2342.511305995244</v>
       </c>
       <c r="E56">
-        <v>738.2600000000001</v>
+        <v>758.35</v>
       </c>
       <c r="F56">
-        <v>1084.86</v>
+        <v>1104.95</v>
       </c>
       <c r="G56">
         <v>50.4</v>
@@ -5867,28 +5867,28 @@
         <v>329.65</v>
       </c>
       <c r="M56">
-        <v>59.99275800000001</v>
+        <v>61.10373500000001</v>
       </c>
       <c r="N56">
-        <v>269.657242</v>
+        <v>268.5462649999999</v>
       </c>
       <c r="O56">
-        <v>80.89717259999999</v>
+        <v>80.56387949999998</v>
       </c>
       <c r="P56">
-        <v>188.7600694</v>
+        <v>187.9823855</v>
       </c>
       <c r="Q56">
-        <v>320.8600694</v>
+        <v>320.0823855</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1720490277533595</v>
+        <v>0.1743925525326581</v>
       </c>
       <c r="T56">
-        <v>0.9705292884423926</v>
+        <v>0.9885449474694327</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.494829892634707</v>
+        <v>5.394923894586802</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09976714863969616</v>
+        <v>0.09948834451284695</v>
       </c>
       <c r="C57">
-        <v>1287.961305995244</v>
+        <v>1275.054853806871</v>
       </c>
       <c r="D57">
-        <v>2342.511305995244</v>
+        <v>2349.694853806871</v>
       </c>
       <c r="E57">
-        <v>758.35</v>
+        <v>778.4400000000002</v>
       </c>
       <c r="F57">
-        <v>1104.95</v>
+        <v>1125.04</v>
       </c>
       <c r="G57">
         <v>50.4</v>
@@ -5949,28 +5949,28 @@
         <v>329.65</v>
       </c>
       <c r="M57">
-        <v>61.10373500000001</v>
+        <v>62.21471200000001</v>
       </c>
       <c r="N57">
-        <v>268.5462649999999</v>
+        <v>267.435288</v>
       </c>
       <c r="O57">
-        <v>80.56387949999998</v>
+        <v>80.23058639999998</v>
       </c>
       <c r="P57">
-        <v>187.9823855</v>
+        <v>187.2047016</v>
       </c>
       <c r="Q57">
-        <v>320.0823855</v>
+        <v>319.3047015999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1743925525326581</v>
+        <v>0.1768426011655613</v>
       </c>
       <c r="T57">
-        <v>0.9885449474694327</v>
+        <v>1.007379500088611</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.394923894586802</v>
+        <v>5.298585967897752</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09948834451284695</v>
+        <v>0.09920954038599775</v>
       </c>
       <c r="C58">
-        <v>1275.054853806871</v>
+        <v>1262.192595294508</v>
       </c>
       <c r="D58">
-        <v>2349.694853806871</v>
+        <v>2356.922595294508</v>
       </c>
       <c r="E58">
-        <v>778.4400000000002</v>
+        <v>798.5300000000001</v>
       </c>
       <c r="F58">
-        <v>1125.04</v>
+        <v>1145.13</v>
       </c>
       <c r="G58">
         <v>50.4</v>
@@ -6031,28 +6031,28 @@
         <v>329.65</v>
       </c>
       <c r="M58">
-        <v>62.21471200000001</v>
+        <v>63.32568900000001</v>
       </c>
       <c r="N58">
-        <v>267.435288</v>
+        <v>266.324311</v>
       </c>
       <c r="O58">
-        <v>80.23058639999998</v>
+        <v>79.89729329999999</v>
       </c>
       <c r="P58">
-        <v>187.2047016</v>
+        <v>186.4270177</v>
       </c>
       <c r="Q58">
-        <v>319.3047015999999</v>
+        <v>318.5270177</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1768426011655613</v>
+        <v>0.179406605548832</v>
       </c>
       <c r="T58">
-        <v>1.007379500088611</v>
+        <v>1.027090078411006</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.298585967897752</v>
+        <v>5.205628319338143</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09920954038599775</v>
+        <v>0.09893073625914853</v>
       </c>
       <c r="C59">
-        <v>1262.192595294508</v>
+        <v>1249.37493954027</v>
       </c>
       <c r="D59">
-        <v>2356.922595294508</v>
+        <v>2364.19493954027</v>
       </c>
       <c r="E59">
-        <v>798.5300000000001</v>
+        <v>818.6200000000002</v>
       </c>
       <c r="F59">
-        <v>1145.13</v>
+        <v>1165.22</v>
       </c>
       <c r="G59">
         <v>50.4</v>
@@ -6113,28 +6113,28 @@
         <v>329.65</v>
       </c>
       <c r="M59">
-        <v>63.32568900000001</v>
+        <v>64.43666600000002</v>
       </c>
       <c r="N59">
-        <v>266.324311</v>
+        <v>265.213334</v>
       </c>
       <c r="O59">
-        <v>79.89729329999999</v>
+        <v>79.5640002</v>
       </c>
       <c r="P59">
-        <v>186.4270177</v>
+        <v>185.6493338</v>
       </c>
       <c r="Q59">
-        <v>318.5270177</v>
+        <v>317.7493337999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.179406605548832</v>
+        <v>0.1820927053789251</v>
       </c>
       <c r="T59">
-        <v>1.027090078411006</v>
+        <v>1.047739255701135</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.205628319338143</v>
+        <v>5.115876106935761</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09893073625914853</v>
+        <v>0.09865193213229931</v>
       </c>
       <c r="C60">
-        <v>1249.37493954027</v>
+        <v>1236.60230069083</v>
       </c>
       <c r="D60">
-        <v>2364.19493954027</v>
+        <v>2371.51230069083</v>
       </c>
       <c r="E60">
-        <v>818.62</v>
+        <v>838.7099999999999</v>
       </c>
       <c r="F60">
-        <v>1165.22</v>
+        <v>1185.31</v>
       </c>
       <c r="G60">
         <v>50.4</v>
@@ -6195,28 +6195,28 @@
         <v>329.65</v>
       </c>
       <c r="M60">
-        <v>64.436666</v>
+        <v>65.54764299999999</v>
       </c>
       <c r="N60">
-        <v>265.213334</v>
+        <v>264.102357</v>
       </c>
       <c r="O60">
-        <v>79.5640002</v>
+        <v>79.23070709999999</v>
       </c>
       <c r="P60">
-        <v>185.6493338</v>
+        <v>184.8716499</v>
       </c>
       <c r="Q60">
-        <v>317.7493337999999</v>
+        <v>316.9716499</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1820927053789251</v>
+        <v>0.1849098344690227</v>
       </c>
       <c r="T60">
-        <v>1.047739255701135</v>
+        <v>1.069395709932246</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.115876106935762</v>
+        <v>5.029166342411427</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09865193213229931</v>
+        <v>0.09837312800545012</v>
       </c>
       <c r="C61">
-        <v>1236.60230069083</v>
+        <v>1223.875098036037</v>
       </c>
       <c r="D61">
-        <v>2371.51230069083</v>
+        <v>2378.875098036036</v>
       </c>
       <c r="E61">
-        <v>838.7099999999999</v>
+        <v>858.7999999999998</v>
       </c>
       <c r="F61">
-        <v>1185.31</v>
+        <v>1205.4</v>
       </c>
       <c r="G61">
         <v>50.4</v>
@@ -6277,28 +6277,28 @@
         <v>329.65</v>
       </c>
       <c r="M61">
-        <v>65.54764299999999</v>
+        <v>66.65862</v>
       </c>
       <c r="N61">
-        <v>264.102357</v>
+        <v>262.99138</v>
       </c>
       <c r="O61">
-        <v>79.23070709999999</v>
+        <v>78.897414</v>
       </c>
       <c r="P61">
-        <v>184.8716499</v>
+        <v>184.093966</v>
       </c>
       <c r="Q61">
-        <v>316.9716499</v>
+        <v>316.193966</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1849098344690227</v>
+        <v>0.1878678200136253</v>
       </c>
       <c r="T61">
-        <v>1.069395709932246</v>
+        <v>1.092134986874912</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.029166342411427</v>
+        <v>4.945346903371236</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09837312800545012</v>
+        <v>0.0980943238786009</v>
       </c>
       <c r="C62">
-        <v>1223.875098036037</v>
+        <v>1211.193756089013</v>
       </c>
       <c r="D62">
-        <v>2378.875098036036</v>
+        <v>2386.283756089013</v>
       </c>
       <c r="E62">
-        <v>858.7999999999998</v>
+        <v>878.89</v>
       </c>
       <c r="F62">
-        <v>1205.4</v>
+        <v>1225.49</v>
       </c>
       <c r="G62">
         <v>50.4</v>
@@ -6359,28 +6359,28 @@
         <v>329.65</v>
       </c>
       <c r="M62">
-        <v>66.65862</v>
+        <v>67.769597</v>
       </c>
       <c r="N62">
-        <v>262.99138</v>
+        <v>261.880403</v>
       </c>
       <c r="O62">
-        <v>78.897414</v>
+        <v>78.56412089999999</v>
       </c>
       <c r="P62">
-        <v>184.093966</v>
+        <v>183.3162821</v>
       </c>
       <c r="Q62">
-        <v>316.193966</v>
+        <v>315.4162821</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1878678200136253</v>
+        <v>0.1909774971246177</v>
       </c>
       <c r="T62">
-        <v>1.092134986874912</v>
+        <v>1.116040380583869</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.945346903371236</v>
+        <v>4.864275642660233</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0980943238786009</v>
+        <v>0.09781551975175171</v>
       </c>
       <c r="C63">
-        <v>1211.193756089013</v>
+        <v>1198.558704667732</v>
       </c>
       <c r="D63">
-        <v>2386.283756089013</v>
+        <v>2393.738704667732</v>
       </c>
       <c r="E63">
-        <v>878.89</v>
+        <v>898.9799999999999</v>
       </c>
       <c r="F63">
-        <v>1225.49</v>
+        <v>1245.58</v>
       </c>
       <c r="G63">
         <v>50.4</v>
@@ -6441,28 +6441,28 @@
         <v>329.65</v>
       </c>
       <c r="M63">
-        <v>67.769597</v>
+        <v>68.880574</v>
       </c>
       <c r="N63">
-        <v>261.880403</v>
+        <v>260.769426</v>
       </c>
       <c r="O63">
-        <v>78.56412089999999</v>
+        <v>78.23082779999999</v>
       </c>
       <c r="P63">
-        <v>183.3162821</v>
+        <v>182.5385982</v>
       </c>
       <c r="Q63">
-        <v>315.4162821</v>
+        <v>314.6385981999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1909774971246177</v>
+        <v>0.1942508414519782</v>
       </c>
       <c r="T63">
-        <v>1.116040380583869</v>
+        <v>1.141203952909086</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.864275642660233</v>
+        <v>4.785819583907648</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09781551975175171</v>
+        <v>0.0975367156249025</v>
       </c>
       <c r="C64">
-        <v>1198.558704667732</v>
+        <v>1185.970378978153</v>
       </c>
       <c r="D64">
-        <v>2393.738704667732</v>
+        <v>2401.240378978153</v>
       </c>
       <c r="E64">
-        <v>898.9799999999999</v>
+        <v>919.0700000000001</v>
       </c>
       <c r="F64">
-        <v>1245.58</v>
+        <v>1265.67</v>
       </c>
       <c r="G64">
         <v>50.4</v>
@@ -6523,28 +6523,28 @@
         <v>329.65</v>
       </c>
       <c r="M64">
-        <v>68.880574</v>
+        <v>69.991551</v>
       </c>
       <c r="N64">
-        <v>260.769426</v>
+        <v>259.658449</v>
       </c>
       <c r="O64">
-        <v>78.23082779999999</v>
+        <v>77.89753469999998</v>
       </c>
       <c r="P64">
-        <v>182.5385982</v>
+        <v>181.7609143</v>
       </c>
       <c r="Q64">
-        <v>314.6385981999999</v>
+        <v>313.8609143</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1942508414519782</v>
+        <v>0.1977011233105473</v>
       </c>
       <c r="T64">
-        <v>1.141203952909086</v>
+        <v>1.167727718332965</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.785819583907648</v>
+        <v>4.709854193686892</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0975367156249025</v>
+        <v>0.0972579114980533</v>
       </c>
       <c r="C65">
-        <v>1185.970378978153</v>
+        <v>1173.429219698905</v>
       </c>
       <c r="D65">
-        <v>2401.240378978153</v>
+        <v>2408.789219698905</v>
       </c>
       <c r="E65">
-        <v>919.0700000000001</v>
+        <v>939.16</v>
       </c>
       <c r="F65">
-        <v>1265.67</v>
+        <v>1285.76</v>
       </c>
       <c r="G65">
         <v>50.4</v>
@@ -6605,28 +6605,28 @@
         <v>329.65</v>
       </c>
       <c r="M65">
-        <v>69.991551</v>
+        <v>71.10252800000001</v>
       </c>
       <c r="N65">
-        <v>259.658449</v>
+        <v>258.547472</v>
       </c>
       <c r="O65">
-        <v>77.89753469999998</v>
+        <v>77.56424159999999</v>
       </c>
       <c r="P65">
-        <v>181.7609143</v>
+        <v>180.9832304</v>
       </c>
       <c r="Q65">
-        <v>313.8609143</v>
+        <v>313.0832303999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1977011233105473</v>
+        <v>0.2013430874945925</v>
       </c>
       <c r="T65">
-        <v>1.167727718332965</v>
+        <v>1.195725026280392</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.709854193686892</v>
+        <v>4.636262721910533</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0972579114980533</v>
+        <v>0.09697910737120408</v>
       </c>
       <c r="C66">
-        <v>1173.429219698905</v>
+        <v>1160.935673067582</v>
       </c>
       <c r="D66">
-        <v>2408.789219698905</v>
+        <v>2416.385673067582</v>
       </c>
       <c r="E66">
-        <v>939.16</v>
+        <v>959.2500000000001</v>
       </c>
       <c r="F66">
-        <v>1285.76</v>
+        <v>1305.85</v>
       </c>
       <c r="G66">
         <v>50.4</v>
@@ -6687,28 +6687,28 @@
         <v>329.65</v>
       </c>
       <c r="M66">
-        <v>71.10252800000001</v>
+        <v>72.21350500000001</v>
       </c>
       <c r="N66">
-        <v>258.547472</v>
+        <v>257.436495</v>
       </c>
       <c r="O66">
-        <v>77.56424159999999</v>
+        <v>77.2309485</v>
       </c>
       <c r="P66">
-        <v>180.9832304</v>
+        <v>180.2055465</v>
       </c>
       <c r="Q66">
-        <v>313.0832303999999</v>
+        <v>312.3055465</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2013430874945925</v>
+        <v>0.2051931639177259</v>
       </c>
       <c r="T66">
-        <v>1.195725026280392</v>
+        <v>1.225322180396243</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.636262721910533</v>
+        <v>4.56493560311191</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09697910737120408</v>
+        <v>0.09785530324435487</v>
       </c>
       <c r="C67">
-        <v>1160.935673067582</v>
+        <v>1117.132085314382</v>
       </c>
       <c r="D67">
-        <v>2416.385673067582</v>
+        <v>2392.672085314382</v>
       </c>
       <c r="E67">
-        <v>959.2500000000001</v>
+        <v>979.34</v>
       </c>
       <c r="F67">
-        <v>1305.85</v>
+        <v>1325.94</v>
       </c>
       <c r="G67">
         <v>50.4</v>
@@ -6769,45 +6769,45 @@
         <v>329.65</v>
       </c>
       <c r="M67">
-        <v>72.21350500000001</v>
+        <v>76.63933200000001</v>
       </c>
       <c r="N67">
-        <v>257.436495</v>
+        <v>253.010668</v>
       </c>
       <c r="O67">
-        <v>77.2309485</v>
+        <v>75.90320039999999</v>
       </c>
       <c r="P67">
-        <v>180.2055465</v>
+        <v>177.1074675999999</v>
       </c>
       <c r="Q67">
-        <v>312.3055465</v>
+        <v>309.2074676</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2051931639177259</v>
+        <v>0.2092697154245731</v>
       </c>
       <c r="T67">
-        <v>1.225322180396243</v>
+        <v>1.256660343577732</v>
       </c>
       <c r="U67">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V67">
         <v>0.3</v>
       </c>
       <c r="W67">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>4.56493560311191</v>
+        <v>4.301316196231981</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09785530324435487</v>
+        <v>0.09759399911750566</v>
       </c>
       <c r="C68">
-        <v>1117.132085314382</v>
+        <v>1104.06523894695</v>
       </c>
       <c r="D68">
-        <v>2392.672085314382</v>
+        <v>2399.69523894695</v>
       </c>
       <c r="E68">
-        <v>979.34</v>
+        <v>999.4299999999999</v>
       </c>
       <c r="F68">
-        <v>1325.94</v>
+        <v>1346.03</v>
       </c>
       <c r="G68">
         <v>50.4</v>
@@ -6851,28 +6851,28 @@
         <v>329.65</v>
       </c>
       <c r="M68">
-        <v>76.63933200000001</v>
+        <v>77.800534</v>
       </c>
       <c r="N68">
-        <v>253.010668</v>
+        <v>251.849466</v>
       </c>
       <c r="O68">
-        <v>75.90320039999999</v>
+        <v>75.5548398</v>
       </c>
       <c r="P68">
-        <v>177.1074675999999</v>
+        <v>176.2946262</v>
       </c>
       <c r="Q68">
-        <v>309.2074676</v>
+        <v>308.3946261999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2092697154245731</v>
+        <v>0.2135933306591081</v>
       </c>
       <c r="T68">
-        <v>1.256660343577732</v>
+        <v>1.289897789376282</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.301316196231981</v>
+        <v>4.237117447034489</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09759399911750566</v>
+        <v>0.09733269499065646</v>
       </c>
       <c r="C69">
-        <v>1104.06523894695</v>
+        <v>1091.039743749249</v>
       </c>
       <c r="D69">
-        <v>2399.69523894695</v>
+        <v>2406.759743749249</v>
       </c>
       <c r="E69">
-        <v>999.4299999999999</v>
+        <v>1019.52</v>
       </c>
       <c r="F69">
-        <v>1346.03</v>
+        <v>1366.12</v>
       </c>
       <c r="G69">
         <v>50.4</v>
@@ -6933,28 +6933,28 @@
         <v>329.65</v>
       </c>
       <c r="M69">
-        <v>77.800534</v>
+        <v>78.96173600000002</v>
       </c>
       <c r="N69">
-        <v>251.849466</v>
+        <v>250.6882639999999</v>
       </c>
       <c r="O69">
-        <v>75.5548398</v>
+        <v>75.20647919999998</v>
       </c>
       <c r="P69">
-        <v>176.2946262</v>
+        <v>175.4817848</v>
       </c>
       <c r="Q69">
-        <v>308.3946261999999</v>
+        <v>307.5817847999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2135933306591081</v>
+        <v>0.2181871718458015</v>
       </c>
       <c r="T69">
-        <v>1.289897789376282</v>
+        <v>1.325212575537241</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.237117447034489</v>
+        <v>4.174806896342805</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09733269499065646</v>
+        <v>0.09707139086380726</v>
       </c>
       <c r="C70">
-        <v>1091.039743749249</v>
+        <v>1078.055966002878</v>
       </c>
       <c r="D70">
-        <v>2406.759743749249</v>
+        <v>2413.865966002877</v>
       </c>
       <c r="E70">
-        <v>1019.52</v>
+        <v>1039.61</v>
       </c>
       <c r="F70">
-        <v>1366.12</v>
+        <v>1386.21</v>
       </c>
       <c r="G70">
         <v>50.4</v>
@@ -7015,28 +7015,28 @@
         <v>329.65</v>
       </c>
       <c r="M70">
-        <v>78.96173600000002</v>
+        <v>80.122938</v>
       </c>
       <c r="N70">
-        <v>250.6882639999999</v>
+        <v>249.527062</v>
       </c>
       <c r="O70">
-        <v>75.20647919999998</v>
+        <v>74.85811859999998</v>
       </c>
       <c r="P70">
-        <v>175.4817848</v>
+        <v>174.6689434</v>
       </c>
       <c r="Q70">
-        <v>307.5817847999999</v>
+        <v>306.7689434</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2181871718458015</v>
+        <v>0.2230773898832492</v>
       </c>
       <c r="T70">
-        <v>1.325212575537241</v>
+        <v>1.362805734998907</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.174806896342805</v>
+        <v>4.114302448569721</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09707139086380726</v>
+        <v>0.09681008673695803</v>
       </c>
       <c r="C71">
-        <v>1078.055966002878</v>
+        <v>1065.114276328194</v>
       </c>
       <c r="D71">
-        <v>2413.865966002877</v>
+        <v>2421.014276328194</v>
       </c>
       <c r="E71">
-        <v>1039.61</v>
+        <v>1059.7</v>
       </c>
       <c r="F71">
-        <v>1386.21</v>
+        <v>1406.3</v>
       </c>
       <c r="G71">
         <v>50.4</v>
@@ -7097,28 +7097,28 @@
         <v>329.65</v>
       </c>
       <c r="M71">
-        <v>80.122938</v>
+        <v>81.28414000000002</v>
       </c>
       <c r="N71">
-        <v>249.527062</v>
+        <v>248.3658599999999</v>
       </c>
       <c r="O71">
-        <v>74.85811859999998</v>
+        <v>74.50975799999998</v>
       </c>
       <c r="P71">
-        <v>174.6689434</v>
+        <v>173.856102</v>
       </c>
       <c r="Q71">
-        <v>306.7689434</v>
+        <v>305.956102</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2230773898832492</v>
+        <v>0.2282936224565268</v>
       </c>
       <c r="T71">
-        <v>1.362805734998907</v>
+        <v>1.402905105091351</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.114302448569721</v>
+        <v>4.055526699304439</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09681008673695803</v>
+        <v>0.09828828261010883</v>
       </c>
       <c r="C72">
-        <v>1065.114276328194</v>
+        <v>1005.134819267924</v>
       </c>
       <c r="D72">
-        <v>2421.014276328194</v>
+        <v>2381.124819267924</v>
       </c>
       <c r="E72">
-        <v>1059.7</v>
+        <v>1079.79</v>
       </c>
       <c r="F72">
-        <v>1406.3</v>
+        <v>1426.39</v>
       </c>
       <c r="G72">
         <v>50.4</v>
@@ -7179,45 +7179,45 @@
         <v>329.65</v>
       </c>
       <c r="M72">
-        <v>81.28414000000002</v>
+        <v>87.437707</v>
       </c>
       <c r="N72">
-        <v>248.3658599999999</v>
+        <v>242.212293</v>
       </c>
       <c r="O72">
-        <v>74.50975799999998</v>
+        <v>72.6636879</v>
       </c>
       <c r="P72">
-        <v>173.856102</v>
+        <v>169.5486051</v>
       </c>
       <c r="Q72">
-        <v>305.956102</v>
+        <v>301.6486050999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2282936224565268</v>
+        <v>0.2338695952072719</v>
       </c>
       <c r="T72">
-        <v>1.402905105091351</v>
+        <v>1.445769948983273</v>
       </c>
       <c r="U72">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V72">
         <v>0.3</v>
       </c>
       <c r="W72">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>4.055526699304439</v>
+        <v>3.770112589983632</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09828828261010883</v>
+        <v>0.09805147848325962</v>
       </c>
       <c r="C73">
-        <v>1005.134819267924</v>
+        <v>991.3463788078125</v>
       </c>
       <c r="D73">
-        <v>2381.124819267924</v>
+        <v>2387.426378807812</v>
       </c>
       <c r="E73">
-        <v>1079.79</v>
+        <v>1099.88</v>
       </c>
       <c r="F73">
-        <v>1426.39</v>
+        <v>1446.48</v>
       </c>
       <c r="G73">
         <v>50.4</v>
@@ -7261,28 +7261,28 @@
         <v>329.65</v>
       </c>
       <c r="M73">
-        <v>87.43770699999999</v>
+        <v>88.669224</v>
       </c>
       <c r="N73">
-        <v>242.212293</v>
+        <v>240.980776</v>
       </c>
       <c r="O73">
-        <v>72.6636879</v>
+        <v>72.29423279999999</v>
       </c>
       <c r="P73">
-        <v>169.5486051</v>
+        <v>168.6865432</v>
       </c>
       <c r="Q73">
-        <v>301.6486050999999</v>
+        <v>300.7865432</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2338695952072718</v>
+        <v>0.2398438517259272</v>
       </c>
       <c r="T73">
-        <v>1.445769948983273</v>
+        <v>1.491696567438904</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.770112589983633</v>
+        <v>3.717749915122749</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09805147848325962</v>
+        <v>0.09781467435641042</v>
       </c>
       <c r="C74">
-        <v>991.3463788078125</v>
+        <v>977.5913805438497</v>
       </c>
       <c r="D74">
-        <v>2387.426378807812</v>
+        <v>2393.76138054385</v>
       </c>
       <c r="E74">
-        <v>1099.88</v>
+        <v>1119.97</v>
       </c>
       <c r="F74">
-        <v>1446.48</v>
+        <v>1466.57</v>
       </c>
       <c r="G74">
         <v>50.4</v>
@@ -7343,28 +7343,28 @@
         <v>329.65</v>
       </c>
       <c r="M74">
-        <v>88.669224</v>
+        <v>89.900741</v>
       </c>
       <c r="N74">
-        <v>240.980776</v>
+        <v>239.749259</v>
       </c>
       <c r="O74">
-        <v>72.29423279999999</v>
+        <v>71.92477769999999</v>
       </c>
       <c r="P74">
-        <v>168.6865432</v>
+        <v>167.8244813</v>
       </c>
       <c r="Q74">
-        <v>300.7865432</v>
+        <v>299.9244813</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2398438517259272</v>
+        <v>0.246260645764483</v>
       </c>
       <c r="T74">
-        <v>1.491696567438904</v>
+        <v>1.54102515763199</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.717749915122749</v>
+        <v>3.66682183409367</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09781467435641042</v>
+        <v>0.09757787022956119</v>
       </c>
       <c r="C75">
-        <v>977.5913805438497</v>
+        <v>963.8700913994805</v>
       </c>
       <c r="D75">
-        <v>2393.76138054385</v>
+        <v>2400.130091399481</v>
       </c>
       <c r="E75">
-        <v>1119.97</v>
+        <v>1140.06</v>
       </c>
       <c r="F75">
-        <v>1466.57</v>
+        <v>1486.66</v>
       </c>
       <c r="G75">
         <v>50.4</v>
@@ -7425,28 +7425,28 @@
         <v>329.65</v>
       </c>
       <c r="M75">
-        <v>89.900741</v>
+        <v>91.13225800000001</v>
       </c>
       <c r="N75">
-        <v>239.749259</v>
+        <v>238.517742</v>
       </c>
       <c r="O75">
-        <v>71.92477769999999</v>
+        <v>71.55532259999998</v>
       </c>
       <c r="P75">
-        <v>167.8244813</v>
+        <v>166.9624194</v>
       </c>
       <c r="Q75">
-        <v>299.9244813</v>
+        <v>299.0624194</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.246260645764483</v>
+        <v>0.2531710393444662</v>
       </c>
       <c r="T75">
-        <v>1.54102515763199</v>
+        <v>1.594148254763005</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.66682183409367</v>
+        <v>3.617270187686998</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09757787022956119</v>
+        <v>0.09734106610271198</v>
       </c>
       <c r="C76">
-        <v>963.8700913994805</v>
+        <v>950.1827811463731</v>
       </c>
       <c r="D76">
-        <v>2400.130091399481</v>
+        <v>2406.532781146373</v>
       </c>
       <c r="E76">
-        <v>1140.06</v>
+        <v>1160.15</v>
       </c>
       <c r="F76">
-        <v>1486.66</v>
+        <v>1506.75</v>
       </c>
       <c r="G76">
         <v>50.4</v>
@@ -7507,28 +7507,28 @@
         <v>329.65</v>
       </c>
       <c r="M76">
-        <v>91.13225800000001</v>
+        <v>92.363775</v>
       </c>
       <c r="N76">
-        <v>238.517742</v>
+        <v>237.286225</v>
       </c>
       <c r="O76">
-        <v>71.55532259999998</v>
+        <v>71.18586749999999</v>
       </c>
       <c r="P76">
-        <v>166.9624194</v>
+        <v>166.1003575</v>
       </c>
       <c r="Q76">
-        <v>299.0624194</v>
+        <v>298.2003575</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2531710393444662</v>
+        <v>0.260634264410848</v>
       </c>
       <c r="T76">
-        <v>1.594148254763005</v>
+        <v>1.651521199664501</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.617270187686998</v>
+        <v>3.569039918517838</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09734106610271198</v>
+        <v>0.09710426197586278</v>
       </c>
       <c r="C77">
-        <v>950.1827811463731</v>
+        <v>936.5297224425169</v>
       </c>
       <c r="D77">
-        <v>2406.532781146373</v>
+        <v>2412.969722442517</v>
       </c>
       <c r="E77">
-        <v>1160.15</v>
+        <v>1180.24</v>
       </c>
       <c r="F77">
-        <v>1506.75</v>
+        <v>1526.84</v>
       </c>
       <c r="G77">
         <v>50.4</v>
@@ -7589,28 +7589,28 @@
         <v>329.65</v>
       </c>
       <c r="M77">
-        <v>92.363775</v>
+        <v>93.595292</v>
       </c>
       <c r="N77">
-        <v>237.286225</v>
+        <v>236.054708</v>
       </c>
       <c r="O77">
-        <v>71.18586749999999</v>
+        <v>70.81641239999999</v>
       </c>
       <c r="P77">
-        <v>166.1003575</v>
+        <v>165.2382956</v>
       </c>
       <c r="Q77">
-        <v>298.2003575</v>
+        <v>297.3382956</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.260634264410848</v>
+        <v>0.2687194248994283</v>
       </c>
       <c r="T77">
-        <v>1.651521199664501</v>
+        <v>1.713675223307789</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.569039918517838</v>
+        <v>3.522078866958393</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09710426197586278</v>
+        <v>0.09837665784901359</v>
       </c>
       <c r="C78">
-        <v>936.5297224425169</v>
+        <v>882.2515944438576</v>
       </c>
       <c r="D78">
-        <v>2412.969722442517</v>
+        <v>2378.781594443858</v>
       </c>
       <c r="E78">
-        <v>1180.24</v>
+        <v>1200.33</v>
       </c>
       <c r="F78">
-        <v>1526.84</v>
+        <v>1546.93</v>
       </c>
       <c r="G78">
         <v>50.4</v>
@@ -7671,45 +7671,45 @@
         <v>329.65</v>
       </c>
       <c r="M78">
-        <v>93.595292</v>
+        <v>99.158213</v>
       </c>
       <c r="N78">
-        <v>236.054708</v>
+        <v>230.491787</v>
       </c>
       <c r="O78">
-        <v>70.81641239999999</v>
+        <v>69.1475361</v>
       </c>
       <c r="P78">
-        <v>165.2382956</v>
+        <v>161.3442509</v>
       </c>
       <c r="Q78">
-        <v>297.3382956</v>
+        <v>293.4442509</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2687194248994283</v>
+        <v>0.2775076428217982</v>
       </c>
       <c r="T78">
-        <v>1.713675223307789</v>
+        <v>1.781233944659188</v>
       </c>
       <c r="U78">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V78">
         <v>0.3</v>
       </c>
       <c r="W78">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>3.522078866958393</v>
+        <v>3.324485083247718</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09837665784901359</v>
+        <v>0.09815945372216438</v>
       </c>
       <c r="C79">
-        <v>882.2515944438576</v>
+        <v>867.9289338274712</v>
       </c>
       <c r="D79">
-        <v>2378.781594443858</v>
+        <v>2384.548933827471</v>
       </c>
       <c r="E79">
-        <v>1200.33</v>
+        <v>1220.42</v>
       </c>
       <c r="F79">
-        <v>1546.93</v>
+        <v>1567.02</v>
       </c>
       <c r="G79">
         <v>50.4</v>
@@ -7753,28 +7753,28 @@
         <v>329.65</v>
       </c>
       <c r="M79">
-        <v>99.158213</v>
+        <v>100.445982</v>
       </c>
       <c r="N79">
-        <v>230.491787</v>
+        <v>229.204018</v>
       </c>
       <c r="O79">
-        <v>69.1475361</v>
+        <v>68.76120539999998</v>
       </c>
       <c r="P79">
-        <v>161.3442509</v>
+        <v>160.4428126</v>
       </c>
       <c r="Q79">
-        <v>293.4442509</v>
+        <v>292.5428125999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2775076428217982</v>
+        <v>0.2870947896462017</v>
       </c>
       <c r="T79">
-        <v>1.781233944659188</v>
+        <v>1.854934367951625</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.324485083247718</v>
+        <v>3.281863479616337</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09815945372216438</v>
+        <v>0.09794224959531517</v>
       </c>
       <c r="C80">
-        <v>867.9289338274712</v>
+        <v>853.6343069268496</v>
       </c>
       <c r="D80">
-        <v>2384.548933827471</v>
+        <v>2390.34430692685</v>
       </c>
       <c r="E80">
-        <v>1220.42</v>
+        <v>1240.51</v>
       </c>
       <c r="F80">
-        <v>1567.02</v>
+        <v>1587.11</v>
       </c>
       <c r="G80">
         <v>50.4</v>
@@ -7835,28 +7835,28 @@
         <v>329.65</v>
       </c>
       <c r="M80">
-        <v>100.445982</v>
+        <v>101.733751</v>
       </c>
       <c r="N80">
-        <v>229.204018</v>
+        <v>227.916249</v>
       </c>
       <c r="O80">
-        <v>68.76120539999998</v>
+        <v>68.37487469999999</v>
       </c>
       <c r="P80">
-        <v>160.4428126</v>
+        <v>159.5413743</v>
       </c>
       <c r="Q80">
-        <v>292.5428125999999</v>
+        <v>291.6413742999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2870947896462017</v>
+        <v>0.2975949980729294</v>
       </c>
       <c r="T80">
-        <v>1.854934367951625</v>
+        <v>1.935653879176674</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.281863479616337</v>
+        <v>3.240320903924991</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09794224959531517</v>
+        <v>0.09772504546846594</v>
       </c>
       <c r="C81">
-        <v>853.6343069268496</v>
+        <v>839.3679186381767</v>
       </c>
       <c r="D81">
-        <v>2390.34430692685</v>
+        <v>2396.167918638177</v>
       </c>
       <c r="E81">
-        <v>1240.51</v>
+        <v>1260.6</v>
       </c>
       <c r="F81">
-        <v>1587.11</v>
+        <v>1607.2</v>
       </c>
       <c r="G81">
         <v>50.4</v>
@@ -7917,28 +7917,28 @@
         <v>329.65</v>
       </c>
       <c r="M81">
-        <v>101.733751</v>
+        <v>103.02152</v>
       </c>
       <c r="N81">
-        <v>227.916249</v>
+        <v>226.62848</v>
       </c>
       <c r="O81">
-        <v>68.37487469999999</v>
+        <v>67.98854399999999</v>
       </c>
       <c r="P81">
-        <v>159.5413743</v>
+        <v>158.639936</v>
       </c>
       <c r="Q81">
-        <v>291.6413742999999</v>
+        <v>290.7399359999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2975949980729294</v>
+        <v>0.3091452273423298</v>
       </c>
       <c r="T81">
-        <v>1.935653879176674</v>
+        <v>2.024445341524227</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.240320903924991</v>
+        <v>3.199816892625928</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09772504546846594</v>
+        <v>0.09750784134161675</v>
       </c>
       <c r="C82">
-        <v>839.3679186381767</v>
+        <v>825.1299758592711</v>
       </c>
       <c r="D82">
-        <v>2396.167918638177</v>
+        <v>2402.019975859271</v>
       </c>
       <c r="E82">
-        <v>1260.6</v>
+        <v>1280.69</v>
       </c>
       <c r="F82">
-        <v>1607.2</v>
+        <v>1627.29</v>
       </c>
       <c r="G82">
         <v>50.4</v>
@@ -7999,28 +7999,28 @@
         <v>329.65</v>
       </c>
       <c r="M82">
-        <v>103.02152</v>
+        <v>104.309289</v>
       </c>
       <c r="N82">
-        <v>226.62848</v>
+        <v>225.3407109999999</v>
       </c>
       <c r="O82">
-        <v>67.98854399999999</v>
+        <v>67.60221329999997</v>
       </c>
       <c r="P82">
-        <v>158.639936</v>
+        <v>157.7384977</v>
       </c>
       <c r="Q82">
-        <v>290.7399359999999</v>
+        <v>289.8384976999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3091452273423298</v>
+        <v>0.3219112702190357</v>
       </c>
       <c r="T82">
-        <v>2.024445341524227</v>
+        <v>2.122583273592577</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.199816892625928</v>
+        <v>3.160312980371287</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09750784134161675</v>
+        <v>0.09729063721476755</v>
       </c>
       <c r="C83">
-        <v>825.1299758592711</v>
+        <v>810.9206875140931</v>
       </c>
       <c r="D83">
-        <v>2402.019975859271</v>
+        <v>2407.900687514093</v>
       </c>
       <c r="E83">
-        <v>1280.69</v>
+        <v>1300.78</v>
       </c>
       <c r="F83">
-        <v>1627.29</v>
+        <v>1647.38</v>
       </c>
       <c r="G83">
         <v>50.4</v>
@@ -8081,28 +8081,28 @@
         <v>329.65</v>
       </c>
       <c r="M83">
-        <v>104.309289</v>
+        <v>105.597058</v>
       </c>
       <c r="N83">
-        <v>225.3407109999999</v>
+        <v>224.052942</v>
       </c>
       <c r="O83">
-        <v>67.60221329999997</v>
+        <v>67.21588259999999</v>
       </c>
       <c r="P83">
-        <v>157.7384977</v>
+        <v>156.8370594</v>
       </c>
       <c r="Q83">
-        <v>289.8384976999999</v>
+        <v>288.9370594</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3219112702190357</v>
+        <v>0.3360957623042642</v>
       </c>
       <c r="T83">
-        <v>2.122583273592577</v>
+        <v>2.231625420335187</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.160312980371287</v>
+        <v>3.121772578171638</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09729063721476755</v>
+        <v>0.09707343308791833</v>
       </c>
       <c r="C84">
-        <v>810.9206875140931</v>
+        <v>796.7402645776028</v>
       </c>
       <c r="D84">
-        <v>2407.900687514093</v>
+        <v>2413.810264577603</v>
       </c>
       <c r="E84">
-        <v>1300.78</v>
+        <v>1320.87</v>
       </c>
       <c r="F84">
-        <v>1647.38</v>
+        <v>1667.47</v>
       </c>
       <c r="G84">
         <v>50.4</v>
@@ -8163,28 +8163,28 @@
         <v>329.65</v>
       </c>
       <c r="M84">
-        <v>105.597058</v>
+        <v>106.884827</v>
       </c>
       <c r="N84">
-        <v>224.052942</v>
+        <v>222.7651729999999</v>
       </c>
       <c r="O84">
-        <v>67.21588259999999</v>
+        <v>66.82955189999998</v>
       </c>
       <c r="P84">
-        <v>156.8370594</v>
+        <v>155.9356211</v>
       </c>
       <c r="Q84">
-        <v>288.9370594</v>
+        <v>288.0356211</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3360957623042642</v>
+        <v>0.3519490181642256</v>
       </c>
       <c r="T84">
-        <v>2.231625420335187</v>
+        <v>2.353496054929868</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.121772578171638</v>
+        <v>3.08416086036234</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09707343308791833</v>
+        <v>0.09685622896106913</v>
       </c>
       <c r="C85">
-        <v>796.7402645776028</v>
+        <v>782.5889201009934</v>
       </c>
       <c r="D85">
-        <v>2413.810264577603</v>
+        <v>2419.748920100993</v>
       </c>
       <c r="E85">
-        <v>1320.87</v>
+        <v>1340.96</v>
       </c>
       <c r="F85">
-        <v>1667.47</v>
+        <v>1687.56</v>
       </c>
       <c r="G85">
         <v>50.4</v>
@@ -8245,28 +8245,28 @@
         <v>329.65</v>
       </c>
       <c r="M85">
-        <v>106.884827</v>
+        <v>108.172596</v>
       </c>
       <c r="N85">
-        <v>222.7651729999999</v>
+        <v>221.477404</v>
       </c>
       <c r="O85">
-        <v>66.82955189999998</v>
+        <v>66.4432212</v>
       </c>
       <c r="P85">
-        <v>155.9356211</v>
+        <v>155.0341828</v>
       </c>
       <c r="Q85">
-        <v>288.0356211</v>
+        <v>287.1341828</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3519490181642256</v>
+        <v>0.3697839310066823</v>
       </c>
       <c r="T85">
-        <v>2.353496054929868</v>
+        <v>2.490600518848886</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.08416086036234</v>
+        <v>3.047444659643741</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09685622896106913</v>
+        <v>0.09663902483421992</v>
       </c>
       <c r="C86">
-        <v>782.5889201009936</v>
+        <v>768.4668692372936</v>
       </c>
       <c r="D86">
-        <v>2419.748920100993</v>
+        <v>2425.716869237293</v>
       </c>
       <c r="E86">
-        <v>1340.96</v>
+        <v>1361.05</v>
       </c>
       <c r="F86">
-        <v>1687.56</v>
+        <v>1707.65</v>
       </c>
       <c r="G86">
         <v>50.4</v>
@@ -8327,28 +8327,28 @@
         <v>329.65</v>
       </c>
       <c r="M86">
-        <v>108.172596</v>
+        <v>109.460365</v>
       </c>
       <c r="N86">
-        <v>221.477404</v>
+        <v>220.189635</v>
       </c>
       <c r="O86">
-        <v>66.4432212</v>
+        <v>66.05689049999999</v>
       </c>
       <c r="P86">
-        <v>155.0341828</v>
+        <v>154.1327445</v>
       </c>
       <c r="Q86">
-        <v>287.1341828</v>
+        <v>286.2327445</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3697839310066821</v>
+        <v>0.3899968322281328</v>
       </c>
       <c r="T86">
-        <v>2.490600518848884</v>
+        <v>2.645985577957104</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.047444659643742</v>
+        <v>3.011592369530286</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09663902483421992</v>
+        <v>0.1011174207073707</v>
       </c>
       <c r="C87">
-        <v>768.4668692372936</v>
+        <v>630.9931912820414</v>
       </c>
       <c r="D87">
-        <v>2425.716869237293</v>
+        <v>2308.333191282041</v>
       </c>
       <c r="E87">
-        <v>1361.05</v>
+        <v>1381.14</v>
       </c>
       <c r="F87">
-        <v>1707.65</v>
+        <v>1727.74</v>
       </c>
       <c r="G87">
         <v>50.4</v>
@@ -8409,45 +8409,45 @@
         <v>329.65</v>
       </c>
       <c r="M87">
-        <v>109.460365</v>
+        <v>124.224506</v>
       </c>
       <c r="N87">
-        <v>220.189635</v>
+        <v>205.425494</v>
       </c>
       <c r="O87">
-        <v>66.05689049999999</v>
+        <v>61.62764819999998</v>
       </c>
       <c r="P87">
-        <v>154.1327445</v>
+        <v>143.7978458</v>
       </c>
       <c r="Q87">
-        <v>286.2327445</v>
+        <v>275.8978458</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3899968322281328</v>
+        <v>0.4130972907669336</v>
       </c>
       <c r="T87">
-        <v>2.645985577957104</v>
+        <v>2.823568502652211</v>
       </c>
       <c r="U87">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V87">
         <v>0.3</v>
       </c>
       <c r="W87">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y87">
-        <v>3.011592369530286</v>
+        <v>2.653663199111453</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1011174207073707</v>
+        <v>0.1009548165805215</v>
       </c>
       <c r="C88">
-        <v>630.9931912820414</v>
+        <v>614.9661173424938</v>
       </c>
       <c r="D88">
-        <v>2308.333191282041</v>
+        <v>2312.396117342494</v>
       </c>
       <c r="E88">
-        <v>1381.14</v>
+        <v>1401.23</v>
       </c>
       <c r="F88">
-        <v>1727.74</v>
+        <v>1747.83</v>
       </c>
       <c r="G88">
         <v>50.4</v>
@@ -8491,28 +8491,28 @@
         <v>329.65</v>
       </c>
       <c r="M88">
-        <v>124.224506</v>
+        <v>125.668977</v>
       </c>
       <c r="N88">
-        <v>205.425494</v>
+        <v>203.981023</v>
       </c>
       <c r="O88">
-        <v>61.62764819999998</v>
+        <v>61.19430689999999</v>
       </c>
       <c r="P88">
-        <v>143.7978458</v>
+        <v>142.7867161</v>
       </c>
       <c r="Q88">
-        <v>275.8978458</v>
+        <v>274.8867161</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4130972907669336</v>
+        <v>0.4397516660040116</v>
       </c>
       <c r="T88">
-        <v>2.823568502652211</v>
+        <v>3.028471877300412</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.653663199111453</v>
+        <v>2.623161323259598</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1009548165805215</v>
+        <v>0.1007922124536723</v>
       </c>
       <c r="C89">
-        <v>614.9661173424938</v>
+        <v>598.9533710349278</v>
       </c>
       <c r="D89">
-        <v>2312.396117342494</v>
+        <v>2316.473371034928</v>
       </c>
       <c r="E89">
-        <v>1401.23</v>
+        <v>1421.32</v>
       </c>
       <c r="F89">
-        <v>1747.83</v>
+        <v>1767.92</v>
       </c>
       <c r="G89">
         <v>50.4</v>
@@ -8573,28 +8573,28 @@
         <v>329.65</v>
       </c>
       <c r="M89">
-        <v>125.668977</v>
+        <v>127.113448</v>
       </c>
       <c r="N89">
-        <v>203.981023</v>
+        <v>202.536552</v>
       </c>
       <c r="O89">
-        <v>61.19430689999999</v>
+        <v>60.76096559999999</v>
       </c>
       <c r="P89">
-        <v>142.7867161</v>
+        <v>141.7755864</v>
       </c>
       <c r="Q89">
-        <v>274.8867161</v>
+        <v>273.8755864</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4397516660040116</v>
+        <v>0.4708484371139359</v>
       </c>
       <c r="T89">
-        <v>3.028471877300412</v>
+        <v>3.267525814389981</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.623161323259598</v>
+        <v>2.59335267185892</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1007922124536723</v>
+        <v>0.1006296083268231</v>
       </c>
       <c r="C90">
-        <v>598.9533710349278</v>
+        <v>582.9550282813377</v>
       </c>
       <c r="D90">
-        <v>2316.473371034928</v>
+        <v>2320.565028281338</v>
       </c>
       <c r="E90">
-        <v>1421.32</v>
+        <v>1441.41</v>
       </c>
       <c r="F90">
-        <v>1767.92</v>
+        <v>1788.01</v>
       </c>
       <c r="G90">
         <v>50.4</v>
@@ -8655,28 +8655,28 @@
         <v>329.65</v>
       </c>
       <c r="M90">
-        <v>127.113448</v>
+        <v>128.557919</v>
       </c>
       <c r="N90">
-        <v>202.536552</v>
+        <v>201.092081</v>
       </c>
       <c r="O90">
-        <v>60.76096559999999</v>
+        <v>60.32762429999999</v>
       </c>
       <c r="P90">
-        <v>141.7755864</v>
+        <v>140.7644567</v>
       </c>
       <c r="Q90">
-        <v>273.8755864</v>
+        <v>272.8644567</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4708484371139359</v>
+        <v>0.5075991666074827</v>
       </c>
       <c r="T90">
-        <v>3.267525814389981</v>
+        <v>3.550044103677652</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.59335267185892</v>
+        <v>2.56421387779309</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1006296083268231</v>
+        <v>0.1004670041999739</v>
       </c>
       <c r="C91">
-        <v>582.9550282813377</v>
+        <v>566.971165541079</v>
       </c>
       <c r="D91">
-        <v>2320.565028281338</v>
+        <v>2324.671165541079</v>
       </c>
       <c r="E91">
-        <v>1441.41</v>
+        <v>1461.5</v>
       </c>
       <c r="F91">
-        <v>1788.01</v>
+        <v>1808.1</v>
       </c>
       <c r="G91">
         <v>50.4</v>
@@ -8737,28 +8737,28 @@
         <v>329.65</v>
       </c>
       <c r="M91">
-        <v>128.557919</v>
+        <v>130.00239</v>
       </c>
       <c r="N91">
-        <v>201.092081</v>
+        <v>199.64761</v>
       </c>
       <c r="O91">
-        <v>60.32762429999999</v>
+        <v>59.89428299999999</v>
       </c>
       <c r="P91">
-        <v>140.7644567</v>
+        <v>139.753327</v>
       </c>
       <c r="Q91">
-        <v>272.8644567</v>
+        <v>271.8533269999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5075991666074827</v>
+        <v>0.5517000419997389</v>
       </c>
       <c r="T91">
-        <v>3.550044103677652</v>
+        <v>3.889066050822858</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.56421387779309</v>
+        <v>2.535722612484277</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1004670041999739</v>
+        <v>0.1003044000731247</v>
       </c>
       <c r="C92">
-        <v>566.971165541079</v>
+        <v>551.0018598156344</v>
       </c>
       <c r="D92">
-        <v>2324.671165541079</v>
+        <v>2328.791859815634</v>
       </c>
       <c r="E92">
-        <v>1461.5</v>
+        <v>1481.59</v>
       </c>
       <c r="F92">
-        <v>1808.1</v>
+        <v>1828.19</v>
       </c>
       <c r="G92">
         <v>50.4</v>
@@ -8819,28 +8819,28 @@
         <v>329.65</v>
       </c>
       <c r="M92">
-        <v>130.00239</v>
+        <v>131.446861</v>
       </c>
       <c r="N92">
-        <v>199.64761</v>
+        <v>198.203139</v>
       </c>
       <c r="O92">
-        <v>59.89428299999999</v>
+        <v>59.46094169999999</v>
       </c>
       <c r="P92">
-        <v>139.753327</v>
+        <v>138.7421973</v>
       </c>
       <c r="Q92">
-        <v>271.8533269999999</v>
+        <v>270.8421973</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5517000419997389</v>
+        <v>0.6056011119236075</v>
       </c>
       <c r="T92">
-        <v>3.889066050822858</v>
+        <v>4.303426208444776</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.535722612484277</v>
+        <v>2.507857528830605</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1003044000731247</v>
+        <v>0.1026533959462755</v>
       </c>
       <c r="C93">
-        <v>551.0018598156344</v>
+        <v>472.767280556973</v>
       </c>
       <c r="D93">
-        <v>2328.791859815634</v>
+        <v>2270.647280556973</v>
       </c>
       <c r="E93">
-        <v>1481.59</v>
+        <v>1501.68</v>
       </c>
       <c r="F93">
-        <v>1828.19</v>
+        <v>1848.28</v>
       </c>
       <c r="G93">
         <v>50.4</v>
@@ -8901,45 +8901,45 @@
         <v>329.65</v>
       </c>
       <c r="M93">
-        <v>131.446861</v>
+        <v>140.099624</v>
       </c>
       <c r="N93">
-        <v>198.203139</v>
+        <v>189.550376</v>
       </c>
       <c r="O93">
-        <v>59.46094169999999</v>
+        <v>56.86511279999999</v>
       </c>
       <c r="P93">
-        <v>138.7421973</v>
+        <v>132.6852632</v>
       </c>
       <c r="Q93">
-        <v>270.8421973</v>
+        <v>264.7852632</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6056011119236075</v>
+        <v>0.6729774493284436</v>
       </c>
       <c r="T93">
-        <v>4.303426208444776</v>
+        <v>4.821376405472175</v>
       </c>
       <c r="U93">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V93">
         <v>0.3</v>
       </c>
       <c r="W93">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.507857528830605</v>
+        <v>2.352968484769095</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1026533959462755</v>
+        <v>0.1025180918194263</v>
       </c>
       <c r="C94">
-        <v>472.767280556973</v>
+        <v>455.9475388716653</v>
       </c>
       <c r="D94">
-        <v>2270.647280556973</v>
+        <v>2273.917538871665</v>
       </c>
       <c r="E94">
-        <v>1501.68</v>
+        <v>1521.77</v>
       </c>
       <c r="F94">
-        <v>1848.28</v>
+        <v>1868.37</v>
       </c>
       <c r="G94">
         <v>50.4</v>
@@ -8983,28 +8983,28 @@
         <v>329.65</v>
       </c>
       <c r="M94">
-        <v>140.099624</v>
+        <v>141.622446</v>
       </c>
       <c r="N94">
-        <v>189.550376</v>
+        <v>188.027554</v>
       </c>
       <c r="O94">
-        <v>56.86511279999999</v>
+        <v>56.40826619999999</v>
       </c>
       <c r="P94">
-        <v>132.6852632</v>
+        <v>131.6192878</v>
       </c>
       <c r="Q94">
-        <v>264.7852632</v>
+        <v>263.7192878</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6729774493284436</v>
+        <v>0.7596041688489469</v>
       </c>
       <c r="T94">
-        <v>4.821376405472175</v>
+        <v>5.487312373078829</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.352968484769095</v>
+        <v>2.327667748373728</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1025180918194263</v>
+        <v>0.1023827876925771</v>
       </c>
       <c r="C95">
-        <v>455.9475388716653</v>
+        <v>439.1372306324411</v>
       </c>
       <c r="D95">
-        <v>2273.917538871665</v>
+        <v>2277.197230632441</v>
       </c>
       <c r="E95">
-        <v>1521.77</v>
+        <v>1541.86</v>
       </c>
       <c r="F95">
-        <v>1868.37</v>
+        <v>1888.46</v>
       </c>
       <c r="G95">
         <v>50.4</v>
@@ -9065,28 +9065,28 @@
         <v>329.65</v>
       </c>
       <c r="M95">
-        <v>141.622446</v>
+        <v>143.145268</v>
       </c>
       <c r="N95">
-        <v>188.027554</v>
+        <v>186.504732</v>
       </c>
       <c r="O95">
-        <v>56.40826619999999</v>
+        <v>55.95141959999999</v>
       </c>
       <c r="P95">
-        <v>131.6192878</v>
+        <v>130.5533124</v>
       </c>
       <c r="Q95">
-        <v>263.7192878</v>
+        <v>262.6533124</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7596041688489469</v>
+        <v>0.8751064615429516</v>
       </c>
       <c r="T95">
-        <v>5.487312373078829</v>
+        <v>6.37522699655437</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.327667748373728</v>
+        <v>2.302905325518688</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1023827876925771</v>
+        <v>0.1022474835657279</v>
       </c>
       <c r="C96">
-        <v>439.1372306324411</v>
+        <v>422.3363967160899</v>
       </c>
       <c r="D96">
-        <v>2277.197230632441</v>
+        <v>2280.48639671609</v>
       </c>
       <c r="E96">
-        <v>1541.86</v>
+        <v>1561.95</v>
       </c>
       <c r="F96">
-        <v>1888.46</v>
+        <v>1908.55</v>
       </c>
       <c r="G96">
         <v>50.4</v>
@@ -9147,28 +9147,28 @@
         <v>329.65</v>
       </c>
       <c r="M96">
-        <v>143.145268</v>
+        <v>144.66809</v>
       </c>
       <c r="N96">
-        <v>186.504732</v>
+        <v>184.9819099999999</v>
       </c>
       <c r="O96">
-        <v>55.95141959999999</v>
+        <v>55.49457299999998</v>
       </c>
       <c r="P96">
-        <v>130.5533124</v>
+        <v>129.487337</v>
       </c>
       <c r="Q96">
-        <v>262.6533124</v>
+        <v>261.5873369999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8751064615429516</v>
+        <v>1.036809671314558</v>
       </c>
       <c r="T96">
-        <v>6.37522699655437</v>
+        <v>7.618307469420128</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.302905325518688</v>
+        <v>2.278664216829018</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1022474835657279</v>
+        <v>0.1021121794388786</v>
       </c>
       <c r="C97">
-        <v>422.3363967160899</v>
+        <v>405.5450782359119</v>
       </c>
       <c r="D97">
-        <v>2280.48639671609</v>
+        <v>2283.785078235912</v>
       </c>
       <c r="E97">
-        <v>1561.95</v>
+        <v>1582.04</v>
       </c>
       <c r="F97">
-        <v>1908.55</v>
+        <v>1928.64</v>
       </c>
       <c r="G97">
         <v>50.4</v>
@@ -9229,28 +9229,28 @@
         <v>329.65</v>
       </c>
       <c r="M97">
-        <v>144.66809</v>
+        <v>146.190912</v>
       </c>
       <c r="N97">
-        <v>184.9819099999999</v>
+        <v>183.459088</v>
       </c>
       <c r="O97">
-        <v>55.49457299999998</v>
+        <v>55.03772639999998</v>
       </c>
       <c r="P97">
-        <v>129.487337</v>
+        <v>128.4213616</v>
       </c>
       <c r="Q97">
-        <v>261.5873369999999</v>
+        <v>260.5213616</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.036809671314558</v>
+        <v>1.279364485971968</v>
       </c>
       <c r="T97">
-        <v>7.618307469420128</v>
+        <v>9.482928178718765</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.278664216829018</v>
+        <v>2.254928131237049</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1021121794388786</v>
+        <v>0.1019768753120294</v>
       </c>
       <c r="C98">
-        <v>405.5450782359121</v>
+        <v>388.7633165434299</v>
       </c>
       <c r="D98">
-        <v>2283.785078235912</v>
+        <v>2287.09331654343</v>
       </c>
       <c r="E98">
-        <v>1582.04</v>
+        <v>1602.13</v>
       </c>
       <c r="F98">
-        <v>1928.64</v>
+        <v>1948.73</v>
       </c>
       <c r="G98">
         <v>50.4</v>
@@ -9311,28 +9311,28 @@
         <v>329.65</v>
       </c>
       <c r="M98">
-        <v>146.190912</v>
+        <v>147.713734</v>
       </c>
       <c r="N98">
-        <v>183.459088</v>
+        <v>181.936266</v>
       </c>
       <c r="O98">
-        <v>55.03772639999999</v>
+        <v>54.58087979999998</v>
       </c>
       <c r="P98">
-        <v>128.4213616</v>
+        <v>127.3553862</v>
       </c>
       <c r="Q98">
-        <v>260.5213616</v>
+        <v>259.4553862</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.279364485971965</v>
+        <v>1.68362251040098</v>
       </c>
       <c r="T98">
-        <v>9.482928178718739</v>
+        <v>12.59062936088312</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.25492813123705</v>
+        <v>2.231681449471719</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1019768753120294</v>
+        <v>0.1018415711851802</v>
       </c>
       <c r="C99">
-        <v>388.7633165434299</v>
+        <v>371.9911532301187</v>
       </c>
       <c r="D99">
-        <v>2287.09331654343</v>
+        <v>2290.411153230119</v>
       </c>
       <c r="E99">
-        <v>1602.13</v>
+        <v>1622.22</v>
       </c>
       <c r="F99">
-        <v>1948.73</v>
+        <v>1968.82</v>
       </c>
       <c r="G99">
         <v>50.4</v>
@@ -9393,28 +9393,28 @@
         <v>329.65</v>
       </c>
       <c r="M99">
-        <v>147.713734</v>
+        <v>149.236556</v>
       </c>
       <c r="N99">
-        <v>181.936266</v>
+        <v>180.413444</v>
       </c>
       <c r="O99">
-        <v>54.58087979999998</v>
+        <v>54.12403319999999</v>
       </c>
       <c r="P99">
-        <v>127.3553862</v>
+        <v>126.2894108</v>
       </c>
       <c r="Q99">
-        <v>259.4553862</v>
+        <v>258.3894108</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.68362251040098</v>
+        <v>2.492138559259009</v>
       </c>
       <c r="T99">
-        <v>12.59062936088312</v>
+        <v>18.80603172521188</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.231681449471719</v>
+        <v>2.208909189783232</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1018415711851802</v>
+        <v>0.101706267058331</v>
       </c>
       <c r="C100">
-        <v>371.9911532301187</v>
+        <v>355.2286301291449</v>
       </c>
       <c r="D100">
-        <v>2290.411153230119</v>
+        <v>2293.738630129145</v>
       </c>
       <c r="E100">
-        <v>1622.22</v>
+        <v>1642.31</v>
       </c>
       <c r="F100">
-        <v>1968.82</v>
+        <v>1988.91</v>
       </c>
       <c r="G100">
         <v>50.4</v>
@@ -9475,28 +9475,28 @@
         <v>329.65</v>
       </c>
       <c r="M100">
-        <v>149.236556</v>
+        <v>150.759378</v>
       </c>
       <c r="N100">
-        <v>180.413444</v>
+        <v>178.890622</v>
       </c>
       <c r="O100">
-        <v>54.12403319999999</v>
+        <v>53.66718659999999</v>
       </c>
       <c r="P100">
-        <v>126.2894108</v>
+        <v>125.2234354</v>
       </c>
       <c r="Q100">
-        <v>258.3894108</v>
+        <v>257.3234354</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.492138559259009</v>
+        <v>4.917686705833097</v>
       </c>
       <c r="T100">
-        <v>18.80603172521188</v>
+        <v>37.45223881819817</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.208909189783232</v>
+        <v>2.186596975745017</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.101706267058331</v>
-      </c>
-      <c r="C101">
-        <v>355.2286301291449</v>
-      </c>
-      <c r="D101">
-        <v>2293.738630129145</v>
-      </c>
-      <c r="E101">
-        <v>1642.31</v>
-      </c>
-      <c r="F101">
-        <v>1988.91</v>
-      </c>
-      <c r="G101">
-        <v>50.4</v>
-      </c>
-      <c r="H101">
-        <v>1662.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>461.7499999999999</v>
-      </c>
-      <c r="K101">
-        <v>132.1</v>
-      </c>
-      <c r="L101">
-        <v>329.65</v>
-      </c>
-      <c r="M101">
-        <v>150.759378</v>
-      </c>
-      <c r="N101">
-        <v>178.890622</v>
-      </c>
-      <c r="O101">
-        <v>53.66718659999999</v>
-      </c>
-      <c r="P101">
-        <v>125.2234354</v>
-      </c>
-      <c r="Q101">
-        <v>257.3234354</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.917686705833097</v>
-      </c>
-      <c r="T101">
-        <v>37.45223881819817</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.05306</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.186596975745017</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
